--- a/results/Int Task Remove ACC -0.3/Rando_fi_all.xlsx
+++ b/results/Int Task Remove ACC -0.3/Rando_fi_all.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.0016702752861119997 +/- 0.00102772952216742</t>
+          <t>0.006742963192081619 +/- 0.0011556784220395485</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -886,157 +886,157 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.020445406742963225 +/- 0.002341174076110885</t>
+          <t>0.01967213114754094 +/- 0.001445508375570414</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.00040210330961950593 +/- 0.0014177750246044858</t>
+          <t>0.008846272811630019 +/- 0.0009503428082732573</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.00046396535725334864 +/- 0.0006069105125378285</t>
+          <t>0.0062171357871945165 +/- 0.0005437177801189683</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.003990102072378643 +/- 0.0012094781810094036</t>
+          <t>0.007980204144757141 +/- 0.0012356934336800616</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.00018558614290129505 +/- 0.0012917174771308994</t>
+          <t>0.006340859882462069 +/- 0.0011343718416883554</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.00012372409526757445 +/- 0.00031543578803542205</t>
+          <t>0.00012372409526751894 +/- 0.00034443330422702394</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.002165171667182153 +/- 0.0018194174042502663</t>
+          <t>0.0038045159294772144 +/- 0.0012831715751742414</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-0.004670584596350102 +/- 0.004335752884673863</t>
+          <t>0.019115372718836954 +/- 0.0042066192390968074</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.004330343334364384 +/- 0.004195688204840867</t>
+          <t>0.029384472626043878 +/- 0.004614842413005442</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.0012681719764924605 +/- 0.0008688259761947506</t>
+          <t>0.004639653572533209 +/- 0.000863856482757134</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.005845963501391926 +/- 0.0010575515618483444</t>
+          <t>0.007206928549334945 +/- 0.0012220690544471455</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-0.008196721311475386 +/- 0.0021396131896716645</t>
+          <t>0.014166408908134809 +/- 0.0012279265846754745</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-0.00513454995360344 +/- 0.002781041360097624</t>
+          <t>0.013083823074543732 +/- 0.00202379682065642</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-0.0039591710485616825 +/- 0.002512086669254185</t>
+          <t>0.0043303433343643396 +/- 0.0032263296777990187</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.001577482214661341 +/- 0.000901255940880551</t>
+          <t>0.006186204763377623 +/- 0.0013693747987119542</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.004794308691617732 +/- 0.001405575968759872</t>
+          <t>0.005474791215589192 +/- 0.0009180836424160752</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>-0.0009279307145066085 +/- 0.0010891937433751158</t>
+          <t>0.005815032477574977 +/- 0.0007922207531621423</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.003402412619857764 +/- 0.0011152339237439023</t>
+          <t>0.014568512217754358 +/- 0.0013009428298677822</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-0.000340241261985752 +/- 0.0003775612624724474</t>
+          <t>0.00012372409526751894 +/- 0.00048315803748262337</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.008908134859263872 +/- 0.0024891307811606206</t>
+          <t>0.015218063717909014 +/- 0.0026456424101878252</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.0013609650479431412 +/- 0.0011254813113925433</t>
+          <t>0.002845654191153668 +/- 0.001033299912681088</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>-0.003216826476956347 +/- 0.0013915523512776984</t>
+          <t>0.0024126198577172466 +/- 0.0010874355602379783</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.0027528611197030982 +/- 0.0010484658989593802</t>
+          <t>0.002721930095886116 +/- 0.001251082487853804</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.004454067429631892 +/- 0.0015904683120547575</t>
+          <t>0.00315496442932256 +/- 0.0016060321665013544</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-9.279307145063643e-05 +/- 0.000554174848969032</t>
+          <t>0.0003402412619857409 +/- 0.0003513088985957477</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.006340859882462135 +/- 0.002222948791689574</t>
+          <t>0.012991030003093063 +/- 0.001901692069154263</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.0003402412619857964 +/- 0.0018374694389457498</t>
+          <t>0.0016393442622950282 +/- 0.0009076028921200792</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0.0008969996906898036 +/- 0.0008797688000821398</t>
+          <t>0.006000618620476306 +/- 0.0010909490930125576</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.008382307454376781 +/- 0.001322821205093921</t>
+          <t>0.014506650170120584 +/- 0.0013443435701887168</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>-0.0006186204763377167 +/- 0.0009381844038418055</t>
+          <t>3.09310238168603e-05 +/- 0.0006554166439968201</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.0002474481905351378 +/- 0.0007551225249448494</t>
+          <t>0.000463965357253282 +/- 0.00034581935934114097</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -1046,122 +1046,122 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.013362202288895786 +/- 0.0014362124053503265</t>
+          <t>0.017166718218372977 +/- 0.002368799504923719</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-9.279307145063643e-05 +/- 0.0016134613493034205</t>
+          <t>0.0033096195484070058 +/- 0.0009076028921200849</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0.0007114135477884531 +/- 0.0007582833697575663</t>
+          <t>-0.000587689452520923 +/- 0.00085774355854391</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.0006804825239715595 +/- 0.0005498419064222374</t>
+          <t>0.0013918960717599238 +/- 0.0008095423648810535</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-0.004206619239096798 +/- 0.001700925095560465</t>
+          <t>0.0018558614290132725 +/- 0.0014962433185830854</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0.0009588617383235575 +/- 0.0011276044623296135</t>
+          <t>0.008103928240024715 +/- 0.001381893467595952</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0.0003402412619857964 +/- 0.0005258274048870954</t>
+          <t>0.0011444478812248303 +/- 0.0007582833697575846</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.0037117228580265784 +/- 0.0014962433185830809</t>
+          <t>0.0014537581193936999 +/- 0.0011326837874172835</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.0026909990720692333 +/- 0.0009588617383235308</t>
+          <t>0.00674296319208163 +/- 0.0010425177572751308</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>-0.00018558614290129505 +/- 0.001276818276557375</t>
+          <t>0.003000309310238103 +/- 0.0010263322006209051</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.002598206000618675 +/- 0.0014846891432106551</t>
+          <t>0.008103928240024682 +/- 0.001715487117087792</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>-0.01394989174141661 +/- 0.0020114680467540023</t>
+          <t>-0.01271265078874113 +/- 0.001286150503327674</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-0.0016084132384781569 +/- 0.0011802526463556447</t>
+          <t>0.0026291370244354573 +/- 0.0014458392691024005</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-0.0021961026909990355 +/- 0.0016739943244954807</t>
+          <t>0.0015156201670274982 +/- 0.00144716208664267</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-0.000618620476337739 +/- 0.000517575024147287</t>
+          <t>0.00012372409526751894 +/- 0.0005212588786375625</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0.000804206619239134 +/- 0.0013210118468334362</t>
+          <t>-0.0016702752861120218 +/- 0.0011589850909493032</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.0030931023816888727 +/- 0.0013339844511505003</t>
+          <t>0.0032477575007732185 +/- 0.001064764273310135</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.0018249304051964565 +/- 0.0009825165588783662</t>
+          <t>0.006062480668110093 +/- 0.0015539569052991674</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.0009588617383235687 +/- 0.0010484658989593774</t>
+          <t>0.000680482523971504 +/- 0.001325350156859169</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>0.001360965047943119 +/- 0.0003711722858026604</t>
+          <t>-0.0003402412619858186 +/- 0.0007757461307754156</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>-0.0005258274048870581 +/- 0.0004598227264868073</t>
+          <t>0.0017630683575625915 +/- 0.0005541748489690413</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0.00021651716671825528 +/- 0.00024157901874131168</t>
+          <t>0.0014228270955767952 +/- 0.00037117228580265673</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0.0038045159294772925 +/- 0.0015092945126824434</t>
+          <t>0.003062171357871901 +/- 0.002104446482298062</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0.004794308691617732 +/- 0.0015665273445221914</t>
+          <t>0.004330343334364295 +/- 0.0011406797967575654</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1171,92 +1171,92 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>-0.00015465511908441254 +/- 0.0006376593915276075</t>
+          <t>0.0007114135477884088 +/- 0.0007707971416255488</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>-0.002721930095886138 +/- 0.0010786016563045272</t>
+          <t>0.0013300340241261589 +/- 0.0007831109743997567</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>-0.001391896071759946 +/- 0.0009998904964580496</t>
+          <t>0.004144757191463 +/- 0.0014255142124098836</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.00015465511908446805 +/- 0.00031694867819236756</t>
+          <t>0.000958861738323502 +/- 0.0003513088985957477</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-0.0037426538818434605 +/- 0.000962844566425813</t>
+          <t>-0.0028456541911538015 +/- 0.0005138647610837073</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-0.0017630683575625805 +/- 0.0013053478407676448</t>
+          <t>0.0060934116919269645 +/- 0.0016015581151870878</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-0.0007732755954221737 +/- 0.0013429194770239736</t>
+          <t>0.001113516857407937 +/- 0.0008322687316469806</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>0.0023198267862666656 +/- 0.001064764273310166</t>
+          <t>0.0014228270955768175 +/- 0.0008660686668728729</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>6.186204763380942e-05 +/- 0.00023146658748988576</t>
+          <t>0.00012372409526753003 +/- 0.0002474481905351017</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>9.279307145069194e-05 +/- 0.0012453338780821339</t>
+          <t>0.004918032786885218 +/- 0.0011276044623296224</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>-0.00012372409526751894 +/- 0.000999411965444083</t>
+          <t>0.004082895143829224 +/- 0.0011220759138396</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.3306690738754695e-17 +/- 0.000633897356384746</t>
+          <t>0.0012372409526755113 +/- 0.0006633965539600224</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.0036807918342097513 +/- 0.0010575515618483718</t>
+          <t>0.0033096195484069945 +/- 0.0012906060034039734</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>0.0015465511908444363 +/- 0.0010714820956194723</t>
+          <t>0.0011444478812248193 +/- 0.00121421505885497</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>0.006804825239715451 +/- 0.0013553295576991533</t>
+          <t>0.003618929786575875 +/- 0.0007831109743997544</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>-0.00015465511908442365 +/- 0.0002851699491893876</t>
+          <t>0.0003093102381688473 +/- 0.00019562497124456238</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0.0006804825239715706 +/- 0.0004545913534394848</t>
+          <t>0.0014846891432105935 +/- 0.0004330343334364281</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.0002474481905351378 +/- 0.000995575437020148</t>
+          <t>3.093102381687141e-05 +/- 0.00025693238054185836</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>-0.000680482523971504 +/- 0.00036071462386917327</t>
+          <t>0.00024744819053507117 +/- 0.000513864761083682</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>-0.00024744819053507117 +/- 0.001900685616546523</t>
+          <t>-0.0014846891432106824 +/- 0.0011556784220395652</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1281,37 +1281,37 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.0004021033096195725 +/- 0.0002783792143519956</t>
+          <t>-0.00018558614290135056 +/- 0.0004417833856197114</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.0007732755954222515 +/- 0.0013641247801546553</t>
+          <t>0.0006495515001545993 +/- 0.0014862992609630643</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.0010825858335911209 +/- 0.0011757858217598637</t>
+          <t>0.005351067120321651 +/- 0.0011070541396952331</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>-0.0010825858335910764 +/- 0.0005035205875688028</t>
+          <t>0.0005567584287039628 +/- 0.0004751714041366074</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>-0.00018558614290130614 +/- 0.0009196454529736011</t>
+          <t>0.002814723167336786 +/- 0.0012329806017936835</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.0012681719764924605 +/- 0.0009727302934436458</t>
+          <t>0.00634085988246208 +/- 0.0012314277288830323</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>-0.001175378905041724 +/- 0.0017266051020047098</t>
+          <t>0.004082895143829213 +/- 0.0006748352684587462</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.0012330066392665317 +/- 0.0017797619911523775</t>
+          <t>0.009832437559279183 +/- 0.002122955670464709</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1331,157 +1331,157 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.0049004110022130894 +/- 0.002083990325346441</t>
+          <t>0.004773948782801141 +/- 0.001645528128950113</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.007050268732216247 +/- 0.0013115693020987306</t>
+          <t>0.003983559911476475 +/- 0.001470718096694661</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.001991779955738249 +/- 0.0006006955422067651</t>
+          <t>0.0015175466329434228 +/- 0.0016354748221786256</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.006892190957951294 +/- 0.0021711393883514863</t>
+          <t>0.003920328801770479 +/- 0.0013050753993392697</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.006892190957951317 +/- 0.0010749288650015825</t>
+          <t>0.0043313310148593185 +/- 0.001696963250119468</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.000916851090736659 +/- 0.0004110022130888454</t>
+          <t>3.161555485303724e-05 +/- 0.00035908367662348186</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.0038254821372115224 +/- 0.001314614156578683</t>
+          <t>-0.007303193171040135 +/- 0.0016455281289501065</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.021340499525766676 +/- 0.003426315245309221</t>
+          <t>0.018178944040467916 +/- 0.0031749636640218473</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.015744546316787855 +/- 0.003667404362946568</t>
+          <t>0.019411950679734447 +/- 0.0031272242855208943</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.009579513120455274 +/- 0.0007353590483473297</t>
+          <t>0.004805564337654134 +/- 0.0022076623775018575</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.0001896933291179237 +/- 0.001750028770546709</t>
+          <t>0.007018653177363265 +/- 0.0009977700814454314</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.0052165665507429735 +/- 0.0013054582878319959</t>
+          <t>0.007303193171040168 +/- 0.0020992823649742427</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.0019285488460322408 +/- 0.0027650509521449478</t>
+          <t>-0.003509326588681616 +/- 0.00239715966958803</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.002971862156180849 +/- 0.001866121348513902</t>
+          <t>0.0064811887448624535 +/- 0.0020647160122991793</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>-9.484666455895629e-05 +/- 0.00137845269406206</t>
+          <t>-0.003382864369269667 +/- 0.0018545696333939514</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.003414479924122671 +/- 0.0012146299533543202</t>
+          <t>0.006702497628833404 +/- 0.0017362668628196209</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>-0.0013594688586784699 +/- 0.0008947816438877598</t>
+          <t>0.0008852355358836772 +/- 0.0009568603193437427</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0.0011697755295605571 +/- 0.001077251029870432</t>
+          <t>0.000758773316471717 +/- 0.0009075371542464101</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.0005374644325008227 +/- 0.0003177323939652532</t>
+          <t>9.48466645589896e-05 +/- 0.0002024383255590636</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.012677837496048028 +/- 0.0027614336678226576</t>
+          <t>0.013468226367372781 +/- 0.001517546632943413</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>-0.003667404362946569 +/- 0.0014842484469561388</t>
+          <t>-0.003477711033828623 +/- 0.000812218310380329</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.0043629465697123 +/- 0.001278770054768071</t>
+          <t>-0.0007271577616187131 +/- 0.0009902282493434004</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.0025608599430919977 +/- 0.0006393850273840122</t>
+          <t>-0.0009484666455896074 +/- 0.0007481605795889635</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.004141637685741395 +/- 0.0014791890692746768</t>
+          <t>0.0024976288333860342 +/- 0.0013740950877079215</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.001359468858678492 +/- 0.0006486969500057915</t>
+          <t>2.2204460492503132e-17 +/- 0.0004471114645504671</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.0005058488776477854 +/- 0.0019084904549840798</t>
+          <t>0.006228264306038589 +/- 0.0016430966121006882</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.0032564021498577176 +/- 0.0012491145283046548</t>
+          <t>-0.001296237748972473 +/- 0.0014859310780904248</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>-0.0003161555485298728 +/- 0.000787220967308812</t>
+          <t>0.0010749288650015898 +/- 0.0011503892126879416</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.013120455263989894 +/- 0.0013130926119061142</t>
+          <t>-0.005659184318684773 +/- 0.0015645707279998086</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>-0.00044261776794183303 +/- 0.00047317829741056573</t>
+          <t>-9.484666455894519e-05 +/- 0.0004253437890317354</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.000600695542206775 +/- 0.0003300760831144579</t>
+          <t>0.0005690799873537932 +/- 0.0004856873694510484</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1491,122 +1491,122 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.005754030983243774 +/- 0.0012709295758610145</t>
+          <t>-0.006323110970597523 +/- 0.0015358783182410607</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.0031299399304457686 +/- 0.0017110413060682562</t>
+          <t>-0.0012646221941194913 +/- 0.0017200721478008753</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>0.00025292443882392047 +/- 0.00023658914870527912</t>
+          <t>0.0002845399936769133 +/- 0.00029826054796257376</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>6.323110970599677e-05 +/- 0.0009977700814454355</t>
+          <t>-0.0004110022130887958 +/- 0.0007076518901549035</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.0027189377173569397 +/- 0.0013353596005022078</t>
+          <t>0.00297186215618086 +/- 0.000764024405538711</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>-0.002213088839709143 +/- 0.002058655781991748</t>
+          <t>-0.005943724312361676 +/- 0.0008807074471820678</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-9.48466645589785e-05 +/- 0.00031773239396525873</t>
+          <t>6.323110970600787e-05 +/- 0.0003686975589532273</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.002529244388238994 +/- 0.0006780781090587138</t>
+          <t>0.0013278533038254992 +/- 0.00096724998677068</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.005943724312361687 +/- 0.0013472826906520668</t>
+          <t>-0.0017388555169142838 +/- 0.0014085785273440312</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.0016756244072083427 +/- 0.0006788147503504127</t>
+          <t>0.0011697755295605571 +/- 0.0011833681487330272</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.004710717673095166 +/- 0.0019563362003673637</t>
+          <t>0.0007271577616187463 +/- 0.0013711823232501648</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.013689535251343666 +/- 0.001720362675992765</t>
+          <t>0.009547897565602292 +/- 0.0018958791464514639</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.004110022130888402 +/- 0.0012958521360682473</t>
+          <t>0.0014226999683844665 +/- 0.0010974742306487358</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.0019917799557382376 +/- 0.0009698300126574648</t>
+          <t>-0.0022447043945621136 +/- 0.0014656120122035115</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-0.0002845399936768911 +/- 0.0006393850273840166</t>
+          <t>0.00037938665823586957 +/- 0.00030976790929914923</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>0.0013910844135314737 +/- 0.0009816107933139384</t>
+          <t>0.004394562124565316 +/- 0.00115255935084149</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.0014226999683844333 +/- 0.0017616986045848966</t>
+          <t>0.0017388555169143172 +/- 0.0016863275818014153</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0.003983559911476442 +/- 0.001575711134287336</t>
+          <t>0.005026873221625072 +/- 0.0013813501280400572</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.0016123932975023792 +/- 0.0009426526409026591</t>
+          <t>-0.00885235535883655 +/- 0.001948913690473911</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-0.0005690799873537711 +/- 0.0008577085024502451</t>
+          <t>0.0006006955422067861 +/- 0.0004110022130888411</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0.0003477711033828768 +/- 0.0005557507376303414</t>
+          <t>0.0002529244388239316 +/- 0.0006601521662289158</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>-0.00031615554852988393 +/- 0.0005998629769526014</t>
+          <t>-0.00044261776794178863 +/- 0.0003224166622568817</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>0.004331331014859297 +/- 0.0013638731969726964</t>
+          <t>3.161555485300394e-05 +/- 0.0018076247055229696</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>0.007050268732216236 +/- 0.001378452694062052</t>
+          <t>0.003983559911476453 +/- 0.0015883473521442245</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1616,107 +1616,107 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>-0.0010433133101486192 +/- 0.0006171110115694988</t>
+          <t>-0.0009168510907366257 +/- 0.0006548313366173957</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>0.002529244388239016 +/- 0.0010293278909958555</t>
+          <t>-0.001580777742649364 +/- 0.0008600360739004489</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>0.0008220044261776805 +/- 0.0015820418593989083</t>
+          <t>-0.009326588681631364 +/- 0.0019501954490409215</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.00022130888397090543 +/- 0.0005107649200570323</t>
+          <t>-0.0006323110970597234 +/- 0.0005475974731485668</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.0011697755295605571 +/- 0.0008250387828453966</t>
+          <t>0.004710717673095166 +/- 0.0006548313366173935</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>0.00885235535883654 +/- 0.0014209424631200904</t>
+          <t>0.0011381599747075644 +/- 0.0015883473521442286</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>0.00983243755927916 +/- 0.0017514560840296751</t>
+          <t>0.0070186531773632765 +/- 0.0020085210463823564</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>0.0010749288650015898 +/- 0.0008964556989413792</t>
+          <t>-0.0006639266519127163 +/- 0.0008767261855113528</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>6.323110970598566e-05 +/- 0.00012646221941197132</t>
+          <t>-0.00018969332911789039 +/- 0.0002529244388238955</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.002244704394562125 +/- 0.0015322947601710561</t>
+          <t>0.000758773316471717 +/- 0.0009505720125433172</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.0020866266202971715 +/- 0.0011240207925786328</t>
+          <t>0.0027505532722099215 +/- 0.0006006955422067627</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-0.00012646221941197132 +/- 0.0006510041189369047</t>
+          <t>0.0013278533038254992 +/- 0.0005439345726868519</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.005595953208978832 +/- 0.0014422377145693346</t>
+          <t>0.003572557698387613 +/- 0.000959468283622738</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>0.0005058488776478077 +/- 0.0007373951179064679</t>
+          <t>0.0009484666455896295 +/- 0.0007744197732479082</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>0.0006006955422067639 +/- 0.001681579025857993</t>
+          <t>6.323110970599677e-05 +/- 0.0011024720691851161</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>3.161555485299283e-05 +/- 0.0003300760831144771</t>
+          <t>-0.00025292443882386496 +/- 0.0003405099467046896</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>-0.0013278533038254881 +/- 0.0005620103962893102</t>
+          <t>6.323110970599677e-05 +/- 0.0009775292338754479</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>-0.000474233322794837 +/- 0.0006962603713419453</t>
+          <t>0.0004742333227948481 +/- 0.0005337319954516025</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>3.161555485299283e-05 +/- 9.484666455897849e-05</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>0.0009168510907366478 +/- 0.001033688442887874</t>
+          <t>-0.00012646221941192692 +/- 0.000619535818598329</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0.0027189377173569397 +/- 0.001050474089524892</t>
+          <t>-0.004141637685741361 +/- 0.0011867419778136775</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1726,37 +1726,37 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>-0.00034777110338286566 +/- 0.00029826054796258205</t>
+          <t>0.0015175466329434228 +/- 0.0005620103962893102</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.002339551059121092 +/- 0.0009917412040061952</t>
+          <t>-0.00502687322162505 +/- 0.0011611993469621896</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0.004236484350300352 +/- 0.0015241189747952982</t>
+          <t>-0.0022763199494150953 +/- 0.0013766387010481903</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>-0.0011697755295605571 +/- 0.0003477711033828727</t>
+          <t>-0.0007587733164716836 +/- 0.0007373951179064583</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.0009800822004426336 +/- 0.000817737411089324</t>
+          <t>0.00120139108441355 +/- 0.0008097533022361962</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.002339551059121092 +/- 0.0010312681903445985</t>
+          <t>0.0018337021814732956 +/- 0.0013172726307935064</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>-0.0013910844135314737 +/- 0.0005690799873537698</t>
+          <t>-0.00034777110338284344 +/- 0.000973943838175738</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-0.004071856287425124 +/- 0.0016022860072167323</t>
+          <t>-0.0005688622754491002 +/- 0.0006483954439433329</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1776,157 +1776,157 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.002724550898203615 +/- 0.0017786044000334372</t>
+          <t>0.00044910179640716974 +/- 0.0012143293287828153</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.0012874251497005718 +/- 0.0015788978291539236</t>
+          <t>0.0003892215568862101 +/- 0.0015032802647464716</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.004491017964071841 +/- 0.0007691756035128678</t>
+          <t>-0.0006287425149700931 +/- 0.0011396925934535635</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.001646706586826363 +/- 0.0014498562889584754</t>
+          <t>0.0010778443113772297 +/- 0.0010976229209474944</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.004970059880239508 +/- 0.0017773439616353987</t>
+          <t>0.0036526946107784284 +/- 0.0015888022947810302</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.000538922155688637 +/- 0.00039720057369524285</t>
+          <t>0.0001796407185628568 +/- 0.0003333990636425171</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.0022754491017963783 +/- 0.0013064325885791285</t>
+          <t>0.003952095808383205 +/- 0.0006393460031156559</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.035508982035928185 +/- 0.0023658378760644705</t>
+          <t>0.03395209580838321 +/- 0.0030391802492094615</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.04541916167664674 +/- 0.00287814730987192</t>
+          <t>0.045059880239520934 +/- 0.0031179440043789977</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.0029940119760479165 +/- 0.0013588988883724853</t>
+          <t>0.0017065868263472673 +/- 0.0012420639827958966</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-0.004431137724550882 +/- 0.001344308043152319</t>
+          <t>-0.0016766467065868484 +/- 0.0011138368405831244</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-0.001017964071856292 +/- 0.003103391262239514</t>
+          <t>0.0012275449101796232 +/- 0.0015640668127675408</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.03200598802395212 +/- 0.003631157671409667</t>
+          <t>0.03835329341317365 +/- 0.002956198337244809</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.0130239520958084 +/- 0.0017876533219794081</t>
+          <t>0.012095808383233509 +/- 0.002292717331625956</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>-0.005329341317365266 +/- 0.0018251198388177649</t>
+          <t>0.0014371257485029764 +/- 0.0009543339790724062</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-0.007574850299401181 +/- 0.0012492602422170679</t>
+          <t>-0.002814371257485049 +/- 0.0012926367152648452</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.0059880239520958 +/- 0.0018211863863168438</t>
+          <t>-0.0015868263473053923 +/- 0.001167664670658674</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.00044910179640721414 +/- 0.0009770759803641245</t>
+          <t>-0.0024850299401197873 +/- 0.0010963972109940456</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>5.988023952098187e-05 +/- 0.0004790419161676676</t>
+          <t>-0.00023952095808386087 +/- 0.0002933520650039744</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.0025449101796407247 +/- 0.0027416061564554273</t>
+          <t>0.009221556886227545 +/- 0.0014408634030558158</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.0015269461077844436 +/- 0.0011783633924643405</t>
+          <t>0.003502994011976035 +/- 0.000898702456275667</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.009790419161676667 +/- 0.001688633371521359</t>
+          <t>0.003532934131736498 +/- 0.0007898746082798061</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.005988023952095823 +/- 0.0017964071856287492</t>
+          <t>0.005209580838323335 +/- 0.0011138368405831376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.010479041916167674 +/- 0.0019030237822839158</t>
+          <t>0.006736526946107757 +/- 0.001021919051848886</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.0005089820359281627 +/- 0.0005688622754490856</t>
+          <t>0.0003293413173652615 +/- 0.0005262992763846412</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.0147305389221557 +/- 0.003431508690274094</t>
+          <t>0.012964071856287418 +/- 0.0013918130897208928</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-0.011616766467065854 +/- 0.0020949527765911137</t>
+          <t>-0.002574850299401199 +/- 0.0014308746281854396</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-0.0028443113772454896 +/- 0.0014985022462565667</t>
+          <t>0.004401197604790408 +/- 0.0016510557699355936</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-0.003413173652694601 +/- 0.001726171892862229</t>
+          <t>-5.988023952097077e-05 +/- 0.001477720081347673</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.000628742514970082 +/- 0.0007627388744225663</t>
+          <t>0.0005988023952095744 +/- 0.0005009940278647291</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.00023952095808379425 +/- 0.0005488114604737629</t>
+          <t>0.00044910179640716974 +/- 0.00044910179640718454</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1936,122 +1936,122 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.003473053892215561 +/- 0.0017157543451370443</t>
+          <t>0.004610778443113761 +/- 0.001191601721085781</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.012245508982035936 +/- 0.0018862275449101733</t>
+          <t>-0.005808383233532943 +/- 0.001271662310275181</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>-0.001766467065868238 +/- 0.0006483954439433252</t>
+          <t>0.0003592814371257358 +/- 0.00047904191616768705</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-0.0009580838323353325 +/- 0.0007185628742514808</t>
+          <t>0.0011676646706586524 +/- 0.0007744022249327956</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.015898203592814387 +/- 0.0012521271656482928</t>
+          <t>0.00895209580838322 +/- 0.0009970554374458982</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.0030538922155688986 +/- 0.0018152702264939064</t>
+          <t>0.0036526946107784176 +/- 0.0008552608896458425</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.00014970059880242692 +/- 0.000736429573428077</t>
+          <t>0.0005089820359281294 +/- 0.0005995504309730919</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.010748502994011987 +/- 0.0014449016182052248</t>
+          <t>0.010958083832335319 +/- 0.0014055921669826805</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.0008682634730538985 +/- 0.0014755953928564825</t>
+          <t>0.004550898203592812 +/- 0.0013641659580711997</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>-0.001676646706586804 +/- 0.0018319830587758513</t>
+          <t>0.0011077844311376927 +/- 0.0014110025949638507</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-0.008622754491017948 +/- 0.0009353592426235462</t>
+          <t>0.0011976047904191489 +/- 0.0012271797324502646</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.005898203592814377 +/- 0.0010547254463358446</t>
+          <t>0.0015868263473053702 +/- 0.0006833959407493028</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.015209580838323378 +/- 0.0008656785805269927</t>
+          <t>0.010209580838323329 +/- 0.0011238517592289353</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-0.0031736526946107625 +/- 0.0009101008475191868</t>
+          <t>0.004191616766467043 +/- 0.0013050595639343219</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.0006287425149701043 +/- 0.0005089820359281327</t>
+          <t>-0.0001796407185629012 +/- 0.0004676796213117866</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.00023952095808386087 +/- 0.0012546303496860562</t>
+          <t>-0.003383233532934149 +/- 0.0013325876098363855</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>-0.00757485029940117 +/- 0.0020440573878680616</t>
+          <t>-0.002095808383233555 +/- 0.0011361476623359455</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-0.011526946107784408 +/- 0.0020883099392182028</t>
+          <t>-0.004820359281437136 +/- 0.0005089820359281281</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.001646706586826363 +/- 0.0025589608602205566</t>
+          <t>0.005838323353293406 +/- 0.0010393146681263305</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-0.0004491017964071586 +/- 0.0006860143255921697</t>
+          <t>0.000748502994011957 +/- 0.0005561130425451094</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>-0.00020958083832334218 +/- 0.0004647956495886111</t>
+          <t>-0.0004790419161676884 +/- 0.0003053305097959549</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>-0.00023952095808381645 +/- 0.00039720057369525624</t>
+          <t>5.988023952093746e-05 +/- 0.00032246495851107114</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.0005988023952095967 +/- 0.001688367925733151</t>
+          <t>-0.0016167664670658777 +/- 0.0015041744535425848</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-0.013982035928143687 +/- 0.00140463522224429</t>
+          <t>-0.0075149700598802546 +/- 0.0014071856287425253</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2061,147 +2061,147 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0.00038922155688624337 +/- 0.0003008944796742734</t>
+          <t>-0.00011976047904193044 +/- 0.0006017889593485534</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.0005988023952095856 +/- 0.0013050595639343195</t>
+          <t>0.009161676646706574 +/- 0.0007235356870416048</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.00458083832335332 +/- 0.001429934603144854</t>
+          <t>0.004940119760479045 +/- 0.0008172062313746158</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.0009580838323353547 +/- 0.0005151092974277029</t>
+          <t>0.001017964071856281 +/- 0.0004864693655470572</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.006616766467065893 +/- 0.0010581195836570259</t>
+          <t>0.0051796407185628725 +/- 0.0013982388537527788</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-0.010329341317365247 +/- 0.001279042476843954</t>
+          <t>-0.0020658682634730695 +/- 0.001469507927162633</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-0.007784431137724523 +/- 0.0019264320888796908</t>
+          <t>-0.0035329341317365424 +/- 0.0008861466219729817</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.0044311377245509044 +/- 0.001247465069221524</t>
+          <t>0.00625748502994008 +/- 0.0015811671768276435</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0.0002095808383233755 +/- 0.000379897531151171</t>
+          <t>5.988023952093746e-05 +/- 0.0002610119127868787</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.004491017964071864 +/- 0.0013588988883724803</t>
+          <t>0.000658682634730523 +/- 0.0012257179335604094</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.00257485029940121 +/- 0.0016022860072167295</t>
+          <t>-0.0010479041916167885 +/- 0.0015044723983713825</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-0.00044910179640716974 +/- 0.0010815803513885374</t>
+          <t>0.00044910179640716974 +/- 0.0008599644680446156</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.005958083832335348 +/- 0.0018332059299211462</t>
+          <t>0.010958083832335309 +/- 0.0017209710015808307</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.0018862275449101796 +/- 0.0008150094364560686</t>
+          <t>0.002514970059880217 +/- 0.0013403011548263147</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>-0.004011976047904176 +/- 0.0011057595995580356</t>
+          <t>0.0013772455089819946 +/- 0.0013200842925178756</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0.0008982035928143839 +/- 0.0004827699250478095</t>
+          <t>-0.00014970059880242692 +/- 0.00024138496252391848</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>-0.0017365269461077858 +/- 0.0007309314739960366</t>
+          <t>-0.00020958083832336438 +/- 0.0007091448672052156</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>-8.982035928142284e-05 +/- 0.0005364213433284184</t>
+          <t>-0.0006886227544910418 +/- 0.0005364213433284208</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
+          <t>5.988023952094856e-05 +/- 0.00011976047904189714</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>0.00038922155688619897 +/- 0.0005844078232318347</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>0.0042215568862275284 +/- 0.001170731424911194</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>-0.0006287425149700376 +/- 0.0007508943834721333</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>-0.002005988023952088 +/- 0.0012054384514489371</t>
-        </is>
-      </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>-5.988023952094856e-05 +/- 0.00011976047904189714</t>
-        </is>
-      </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>2.2204460492503132e-17 +/- 0.0002677925721556581</t>
+          <t>-2.994011976050759e-05 +/- 0.00034005439196409964</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.0013473053892215758 +/- 0.0012720147177393859</t>
+          <t>-0.0003592814371257691 +/- 0.0010943513103291544</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>-0.0024850299401197318 +/- 0.001190472775573109</t>
+          <t>0.003293413173652682 +/- 0.0007807428030182678</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>-0.006856287425149687 +/- 0.0012874251497006102</t>
+          <t>-0.002395209580838331 +/- 0.0007455029699394559</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.0001796407185628901 +/- 0.0010811658733693122</t>
+          <t>0.0010778443113772184 +/- 0.0008166575866458771</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.0026946107784431295 +/- 0.001567215847700879</t>
+          <t>0.005389221556886215 +/- 0.001325505606058607</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>-0.00044910179640718085 +/- 0.0009585515325498313</t>
+          <t>-0.0014970059880239695 +/- 0.0007921411110971743</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.0010475905417539622 +/- 0.0011534180705176668</t>
+          <t>0.009577970667464807 +/- 0.002858386443894248</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2221,157 +2221,157 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.009607901825800647 +/- 0.0017730264255755859</t>
+          <t>0.018078419634839915 +/- 0.001903395761219346</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.0013768332834480645 +/- 0.0015448653577448542</t>
+          <t>0.004399880275366641 +/- 0.0019492056456348254</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.004788985333732398 +/- 0.0014354479267622577</t>
+          <t>0.005088296917090673 +/- 0.0012121195289623774</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.007961688117330112 +/- 0.001821625148722285</t>
+          <t>0.009218796767434867 +/- 0.0020900437294338256</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.010625561209218804 +/- 0.0011456246159236932</t>
+          <t>0.007662376533971849 +/- 0.002917942557786054</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.00017958695001496494 +/- 0.0004675396393838149</t>
+          <t>0.00041903621670158486 +/- 0.00030523912083763944</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.005656988925471396 +/- 0.0014568205356046589</t>
+          <t>0.0024842861418736817 +/- 0.0023607697140629663</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.03804250224483685 +/- 0.0018521075731104371</t>
+          <t>0.03612690811134389 +/- 0.003162096201113963</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.033852140077821 +/- 0.002688644498089769</t>
+          <t>0.022837473810236486 +/- 0.0009749474693147126</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-0.0019155941334929594 +/- 0.0016729348832663358</t>
+          <t>0.0011972463334330996 +/- 0.0019627173074833817</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>-0.00014965579167913745 +/- 0.0009767835302053674</t>
+          <t>0.002873391200239439 +/- 0.0016729348832663358</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.003950912900329229 +/- 0.001363757647398321</t>
+          <t>0.006584854833882048 +/- 0.0028740146983915623</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.02244836875187073 +/- 0.002166652028836132</t>
+          <t>0.03472014366956 +/- 0.002283415878211384</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.003531876683627644 +/- 0.0024345644307288456</t>
+          <t>0.022747680335229004 +/- 0.0022518099818981097</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.0026638730918886466 +/- 0.00097861614631977</t>
+          <t>0.011553427117629434 +/- 0.0019267856257924362</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.005926369350493843 +/- 0.00143419916799891</t>
+          <t>0.008979347500748247 +/- 0.0014229110235264495</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>-0.0023346303501945442 +/- 0.0011342289926067853</t>
+          <t>0.0009877282250823072 +/- 0.0015087797858280173</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.005387608500448948 +/- 0.0005184228696704194</t>
+          <t>0.0019155941334929594 +/- 0.0020353187668362693</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.00041903621670158486 +/- 0.0003591739000299299</t>
+          <t>0.00020951810835079243 +/- 0.0002693804250224474</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.017958695001496605 +/- 0.0035566478964412797</t>
+          <t>0.03208620173600718 +/- 0.002669751945043721</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.013947919784495721 +/- 0.0019360624518163629</t>
+          <t>0.0008680035917389972 +/- 0.0018856629751571319</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.0061957497755162905 +/- 0.0017911241305450017</t>
+          <t>0.003711463633642609 +/- 0.0008273136762098298</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.004070637533672539 +/- 0.0012209564833505577</t>
+          <t>0.0009577970667464797 +/- 0.001643762971295532</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00787189464232264 +/- 0.0019120833587170948</t>
+          <t>-0.0029631846752469215 +/- 0.0013939695926004163</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.0008680035917389972 +/- 0.0004529406150979199</t>
+          <t>0.001287039808440582 +/- 0.0006961809847119405</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.0033822208919485064 +/- 0.002984273079515951</t>
+          <t>0.012630948817719246 +/- 0.003446115046901985</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.010894941634241262 +/- 0.0017717627760489771</t>
+          <t>0.006345405567195428 +/- 0.0014216512525636485</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.0030230469919185765 +/- 0.0013281477241744216</t>
+          <t>0.010894941634241206 +/- 0.0012783092789022774</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.003292427416941024 +/- 0.0020951810835079243</t>
+          <t>0.016162825501346945 +/- 0.001944373752638346</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.001227177491768927 +/- 0.0004909074967631448</t>
+          <t>0.00014965579167913745 +/- 0.0009675683852286474</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.0009877282250823072 +/- 0.0005686920083807223</t>
+          <t>5.986231667165498e-05 +/- 0.0005803866934949192</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -2381,217 +2381,217 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.0010775217000897896 +/- 0.0016513755431468032</t>
+          <t>0.00835079317569587 +/- 0.002109881298841909</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.00882969170906912 +/- 0.0014244841705227077</t>
+          <t>0.006345405567195428 +/- 0.0012253510619849534</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>-5.986231667165498e-05 +/- 0.00039708168696263253</t>
+          <t>0.0016162825501346845 +/- 0.0010034752837018949</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-0.001227177491768927 +/- 0.0008513297008876289</t>
+          <t>-0.0005686920083807223 +/- 0.0013077552993087938</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.0075426519006285275 +/- 0.002581030965257112</t>
+          <t>0.007303202633941908 +/- 0.002432355540725528</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.001227177491768927 +/- 0.0018998624450833035</t>
+          <t>-0.0014965579167913745 +/- 0.0018008511172093707</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.0026638730918886466 +/- 0.0005088296917090673</t>
+          <t>0.0005387608500448948 +/- 0.00047889853337323984</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.006375336725531255 +/- 0.002073907476961382</t>
+          <t>0.0008380724334031697 +/- 0.001621815885560493</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.00787189464232263 +/- 0.0014105802655430275</t>
+          <t>-0.003052978150254404 +/- 0.0017235773778973861</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.0017958695001496494 +/- 0.0011897400128315905</t>
+          <t>0.0010775217000897896 +/- 0.0024027096366823594</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.0012571086501047546 +/- 0.0018920659238885428</t>
+          <t>0.003980844058665056 +/- 0.000993155344090811</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.012331637234360992 +/- 0.001632826303141121</t>
+          <t>0.014606405267883881 +/- 0.0026831409555241248</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-0.0031427716252618865 +/- 0.0016076682432799446</t>
+          <t>-0.001825800658485477 +/- 0.001406764441783892</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.00017958695001496494 +/- 0.001579276379320308</t>
+          <t>0.0009877282250823072 +/- 0.0015555565950537249</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.0011972463334330996 +/- 0.00042329050056063753</t>
+          <t>-0.00041903621670158486 +/- 0.0007233191244294839</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.001346902125112237 +/- 0.0019684146120870784</t>
+          <t>0.010954803950912861 +/- 0.0011373840167614446</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>-0.009847351092487244 +/- 0.0012373556784552118</t>
+          <t>-0.002125112241843752 +/- 0.001419443963050504</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.0063154744088596 +/- 0.001287039808440582</t>
+          <t>0.005208021550433983 +/- 0.0015448653577448542</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.010026938042502242 +/- 0.001498053727176589</t>
+          <t>0.005537264292128086 +/- 0.001590862887269472</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.00044896737503741235 +/- 0.0009103206420679733</t>
+          <t>2.993115833582749e-05 +/- 0.0007264089254421762</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.003292427416941024 +/- 0.0005986231667165498</t>
+          <t>-0.001287039808440582 +/- 0.0006141360230075761</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>-0.00020951810835079243 +/- 0.00013716179871163794</t>
+          <t>0.0 +/- 0.0002993115833582749</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.003292427416941024 +/- 0.001290862535339584</t>
+          <t>0.001586351391798857 +/- 0.0017300623785236006</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-0.007363064950613563 +/- 0.0019080966717161534</t>
+          <t>0.003591739000299299 +/- 0.0016284310695881944</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2.993115833582749e-05 +/- 8.979347500748247e-05</t>
+          <t>-2.993115833582749e-05 +/- 8.979347500748247e-05</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>-0.0002693804250224474 +/- 0.0006199435850705749</t>
+          <t>-0.0006285543250523773 +/- 0.0006342298743016168</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.0023046991918587167 +/- 0.002003599876824843</t>
+          <t>0.0019155941334929594 +/- 0.0014178652238643484</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.0059563005088296705 +/- 0.0022175332465718517</t>
+          <t>0.0024244238252020267 +/- 0.0013939695926004163</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>-0.0006584854833882048 +/- 0.0009157173625129184</t>
+          <t>-0.001526489075127202 +/- 0.0007969785666383897</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.0002693804250224474 +/- 0.0018179329109919379</t>
+          <t>0.0037713259503142638 +/- 0.0009945074963086556</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-0.0047291230170607435 +/- 0.002051103465909818</t>
+          <t>0.00835079317569587 +/- 0.0016742731243276799</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.00047889853337323984 +/- 0.0019953107826996587</t>
+          <t>0.0075426519006285275 +/- 0.002124058066352602</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.005118228075426501 +/- 0.0017475798356174736</t>
+          <t>0.0010176593834181347 +/- 0.0013663827848564246</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>-0.00023944926668661992 +/- 0.0002239842793638987</t>
+          <t>0.00041903621670158486 +/- 0.0004675396393838148</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.0033223585752768514 +/- 0.002241641944729448</t>
+          <t>0.00041903621670158486 +/- 0.002065900500058346</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>-0.001586351391798857 +/- 0.001352212750443158</t>
+          <t>0.0015564202334630295 +/- 0.0016600328792411852</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.0046093983837174335 +/- 0.0009196223583200935</t>
+          <t>-0.0024842861418736817 +/- 0.0010110353639062842</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.001287039808440582 +/- 0.0015953616248113</t>
+          <t>0.0008680035917389972 +/- 0.0017269526173901953</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.0013169709667764096 +/- 0.001776811982000093</t>
+          <t>0.0003591739000299299 +/- 0.0016107302061746378</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.00011972463334330996 +/- 0.0011373840167614446</t>
+          <t>-0.008650104759054145 +/- 0.0021643766764191394</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>-0.00011972463334330996 +/- 0.00030523912083763944</t>
+          <t>0.00020951810835079243 +/- 0.0005527143164507429</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.0008380724334031697 +/- 0.0010351162206399594</t>
+          <t>0.001346902125112237 +/- 0.0009949578053633406</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.001346902125112237 +/- 0.0005872917351196802</t>
+          <t>0.00017958695001496494 +/- 0.0011054286329014859</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2601,52 +2601,52 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>-0.0011673151750972721 +/- 0.0007386388913051794</t>
+          <t>-0.0011673151750972721 +/- 0.0007264089254421763</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.0005387608500448948 +/- 0.0008858813880244651</t>
+          <t>0.00023944926668661992 +/- 0.001396217155305664</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>-5.986231667165498e-05 +/- 0.00011972463334330997</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>-0.0006884166417240323 +/- 0.0008680035917389972</t>
+          <t>-0.0019455252918287869 +/- 0.0006987499269637061</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.0026040107752169916 +/- 0.001219855364999387</t>
+          <t>0.0038611194253217462 +/- 0.0019045720766157409</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.0032624962586051964 +/- 0.0012227894771514771</t>
+          <t>-0.0008380724334031697 +/- 0.0012684597486032336</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.00047889853337323984 +/- 0.0007476800955879528</t>
+          <t>-0.0018856629751571319 +/- 0.000721458892139713</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>-0.00014965579167913745 +/- 0.0014739386114630455</t>
+          <t>-0.0030230469919185765 +/- 0.0025658877186647967</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>-0.002933253516911094 +/- 0.0015191352936784765</t>
+          <t>0.0003591739000299299 +/- 0.0024234998479493674</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.0003591739000299299 +/- 0.0016600328792411852</t>
+          <t>-0.00011972463334330996 +/- 0.001521492370803806</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.004297994269340999 +/- 0.000701137075630208</t>
+          <t>0.003247373447946467 +/- 0.0009843759843196573</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2666,157 +2666,157 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.0070041388092963565 +/- 0.001585469544474852</t>
+          <t>-0.0019420566698504116 +/- 0.0010977994046206159</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.004202483285577796 +/- 0.001119286585880094</t>
+          <t>0.0028016555237185157 +/- 0.0008637160118593123</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.001368990767271583 +/- 0.0020288435487239697</t>
+          <t>0.0015918497293855194 +/- 0.0011912312597179</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.0033110474371219724 +/- 0.0009572299508674123</t>
+          <t>0.0003183699458770728 +/- 0.0013432042731441737</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.005635148042024885 +/- 0.0011831202913761163</t>
+          <t>0.008659662527857326 +/- 0.0013264989911492906</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-9.551098376312517e-05 +/- 0.00020385623169157403</t>
+          <t>-0.0005412289079911425 +/- 0.0002038562316916035</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.0020694046482011676 +/- 0.0012268608002545653</t>
+          <t>0.007672715695638299 +/- 0.0014198728507467668</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.018242597898758383 +/- 0.0018837710528477637</t>
+          <t>0.011970709964979287 +/- 0.0014037190503055571</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.021267112384590937 +/- 0.0016032700811224592</t>
+          <t>0.02690226042661571 +/- 0.0017394190868701197</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-0.003820439350525273 +/- 0.0007398248989889893</t>
+          <t>-0.0017191977077364196 +/- 0.0008683974337463301</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>-0.0023241006049028678 +/- 0.001216906389915097</t>
+          <t>0.004043298312639254 +/- 0.0009232728430436268</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.0021649156319643813 +/- 0.001590575739802189</t>
+          <t>-0.0017828716969118363 +/- 0.0015544801802908218</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.004743712193568972 +/- 0.0016073741561750186</t>
+          <t>0.0013371537726838301 +/- 0.0018607627120283364</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.0056033110474371425 +/- 0.0013371537726838576</t>
+          <t>0.0031518624641833524 +/- 0.0016933570387739306</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0.0007959248646927985 +/- 0.0014326647564469911</t>
+          <t>0.003597580388411281 +/- 0.0009122285120594816</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0.0007004138809296623 +/- 0.0010539920634986702</t>
+          <t>0.0023241006049028678 +/- 0.0011124740661990352</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>0.0016555237185610027 +/- 0.0010917814835709777</t>
+          <t>0.0028016555237185157 +/- 0.0007640878701050718</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.002037567653613526 +/- 0.0010578317558634894</t>
+          <t>0.0015918497293855194 +/- 0.0010654696294607824</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.00022285896211402534 +/- 0.0002865329512894224</t>
+          <t>-0.0003502069404649033 +/- 9.551098376312519e-05</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0009232728430435877 +/- 0.001125157405098544</t>
+          <t>-0.0016873607131487113 +/- 0.0015469634655531652</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.0014008277618592468 +/- 0.001048206153018421</t>
+          <t>-0.0005093919134034231 +/- 0.0005730659025787831</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.0015600127347978553 +/- 0.0010112945032962999</t>
+          <t>-0.00019102196752631694 +/- 0.0004764925038871718</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-0.0005412289079910537 +/- 0.0008782626058028635</t>
+          <t>-0.00019102196752630586 +/- 0.0005730659025788003</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.001591849729385597 +/- 0.0007927347722374093</t>
+          <t>-0.0003183699458771727 +/- 0.0005870451739760014</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.0004457179242280063 +/- 0.0003820439350525266</t>
+          <t>0.00022285896211393652 +/- 0.0004039661744810481</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>-6.367398917539457e-05 +/- 0.0016469299148523066</t>
+          <t>0.0022285896211396983 +/- 0.001328026336492461</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-0.004170646290990077 +/- 0.0006594178661957532</t>
+          <t>-0.0032473734479465445 +/- 0.0008277618592804856</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-0.0013371537726838412 +/- 0.0006006992124837195</t>
+          <t>-0.0017191977077364196 +/- 0.0007425599356695779</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-0.0016555237185609361 +/- 0.0006335481930000773</t>
+          <t>-0.0002546959567017226 +/- 0.0007370797136447029</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0003820439350525784 +/- 0.00044571792422796184</t>
+          <t>-0.0004457179242280063 +/- 0.000407712463383181</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.0005412289079910426 +/- 0.0001458954375980731</t>
+          <t>-0.0008595988538682486 +/- 0.0004513672995465619</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -2826,122 +2826,122 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.0019738936644380423 +/- 0.0008518999146933938</t>
+          <t>-0.0015600127347978777 +/- 0.0011693325483735778</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.0022922636103151484 +/- 0.0013641697093682503</t>
+          <t>-0.0065584208850684835 +/- 0.0005904882836991982</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>-0.00044571792422791744 +/- 0.00021118273100000868</t>
+          <t>-0.0007640878701051124 +/- 0.0002917908751961462</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-0.00031836994587706167 +/- 0.0005133561125946163</t>
+          <t>-0.0008277618592805291 +/- 0.0002917908751961462</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0.0011779687997453547 +/- 0.0011658601352181226</t>
+          <t>-0.0007959248646928097 +/- 0.0008209994879482614</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>0.0002546959567017226 +/- 0.0008277618592804865</t>
+          <t>0.0002546959567016449 +/- 0.0006173422295340873</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-0.00025469595670165603 +/- 0.00031193756673456144</t>
+          <t>-9.551098376316957e-05 +/- 0.0004513672995465815</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.0005093919134033454 +/- 0.0007004138809296371</t>
+          <t>-0.0006049028971665593 +/- 0.0004817811509207657</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.0013371537726838301 +/- 0.0005289158779317483</t>
+          <t>-0.0002546959567017226 +/- 0.0008399176032010821</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.001050620821394488 +/- 0.0008185265923070637</t>
+          <t>-0.0013053167780961883 +/- 0.0008942739194643783</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.004520853231454958 +/- 0.000827761859280484</t>
+          <t>0.00012734797835080026 +/- 0.0007560867295153099</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>-0.0014645017510346524 +/- 0.0011047024242532742</t>
+          <t>-0.003724928366762226 +/- 0.0009232728430436172</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-0.01165234001910217 +/- 0.001038491335899432</t>
+          <t>-0.006813116841770173 +/- 0.0009677608502751291</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-0.0012098057943329631 +/- 0.0007640878701050698</t>
+          <t>-0.0041706462909901765 +/- 0.0010212680631865934</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-9.551098376310296e-05 +/- 0.0005879078418535473</t>
+          <t>-0.000732250875517404 +/- 0.00031995783575676826</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>-0.0010824578159821408 +/- 0.001008785706319971</t>
+          <t>-0.001146131805157624 +/- 0.0007560867295153015</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.007768226679401502 +/- 0.0011229030301527158</t>
+          <t>0.0003502069404647923 +/- 0.0016509254584481461</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>0.004106972301814749 +/- 0.0012928328878858341</t>
+          <t>-0.0013371537726838856 +/- 0.001146131805157581</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.007704552690226085 +/- 0.0012231373901495457</t>
+          <t>0.004075135307226951 +/- 0.0011809765673983603</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-0.0002546959567016338 +/- 0.0004223654620000625</t>
+          <t>-0.0007322508755173817 +/- 0.0007266929137544338</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>-0.0010187838268067239 +/- 0.0005835817503923408</t>
+          <t>-0.0006049028971665482 +/- 0.0005221655353981743</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>-0.002929003502069383 +/- 0.00042236546200003573</t>
+          <t>-0.0010824578159821963 +/- 0.0002917908751961462</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.0004775549188157036 +/- 0.0010291773241161827</t>
+          <t>0.0010187838268067239 +/- 0.0009529850077743341</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-0.0011461318051575685 +/- 0.0010578317558635067</t>
+          <t>0.004075135307226962 +/- 0.001464501751034695</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2951,147 +2951,147 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>-0.002228589621139754 +/- 0.00047221894219011645</t>
+          <t>-0.001368990767271594 +/- 0.0005704066497029145</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>-0.008341292581980242 +/- 0.0008028984535446477</t>
+          <t>-0.001146131805157624 +/- 0.0008799920382734999</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>0.004807386182744377 +/- 0.0009055372590466578</t>
+          <t>0.0006685768863419095 +/- 0.00070402242558091</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>-0.0028334925183062577 +/- 0.00043768631279423464</t>
+          <t>-0.0003183699458771394 +/- 0.0003767004000700339</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-0.011079274116523364 +/- 0.000547744365937133</t>
+          <t>-0.005826170009551146 +/- 0.0006375353197867175</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>0.002451448583253768 +/- 0.00047329095024891744</t>
+          <t>0.002865329512893933 +/- 0.0011997098810198625</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-0.0021967526265520344 +/- 0.0009385165853539339</t>
+          <t>-0.001050620821394488 +/- 0.00124977946045149</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-0.0030881884750079357 +/- 0.0008782626058028222</t>
+          <t>0.0021967526265520123 +/- 0.0008477253712635605</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
+          <t>-0.0002865329512894754 +/- 9.551098376315847e-05</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>-0.010792741165234043 +/- 0.0011161125847155592</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>-0.0025151225724291846 +/- 0.00036159874853867064</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>0.0004457179242279063 +/- 0.0007287821166672751</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>-0.009646609360076452 +/- 0.0018621240134848356</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>-0.0008595988538682153 +/- 0.0008548692506907026</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>-0.011556829035339089 +/- 0.0013953904489532704</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>-1.1102230246251566e-17 +/- 0.00014237936819484252</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>0.00015918497293851975 +/- 0.00035594842048707406</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>-0.0008277618592805403 +/- 0.000497309753321007</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>-0.0018465456860871864 +/- 0.00111928658588011</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>-0.004170646290990088 +/- 0.0004138809296402552</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>-0.0004457179242279063 +/- 0.0005365265694477207</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>-0.009137217446672997 +/- 0.0014799922698719424</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>-0.004520853231454913 +/- 0.000583581750392342</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>-0.007481693728112027 +/- 0.0014326647564469836</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>0.0005730659025787622 +/- 0.000467906350101866</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>-0.003183699458771105 +/- 0.0011301012002100485</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
         <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>-0.0009232728430435988 +/- 0.0005596432929400521</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>-0.0033747214262973223 +/- 0.0006857898512746892</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>-0.00019102196752622812 +/- 0.0004547232364560837</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>-0.012098057943330121 +/- 0.0008302072467625341</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>-0.00044571792422791744 +/- 0.0002546959567016671</t>
+          <t>0.0003183699458770728 +/- 0.00034875680197717573</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>-0.003820439350525273 +/- 0.0014658853146413717</t>
+          <t>0.0011142948105698491 +/- 0.0008332538890991697</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>-0.00719516077682264 +/- 0.0014393702076354502</t>
+          <t>-0.0029290035020694384 +/- 0.0013416942060302695</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>-0.0002865329512893533 +/- 0.0007726622794977156</t>
+          <t>-0.0007004138809296844 +/- 0.0004457179242279349</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>-0.008659662527857348 +/- 0.0007901734254053571</t>
+          <t>-0.002578796561604624 +/- 0.000811062668122076</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>-0.0031836994587710723 +/- 0.0010267122251892361</t>
+          <t>-0.0014645017510347303 +/- 0.0010954887318742543</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>-0.009678446354664083 +/- 0.0009986874970619667</t>
+          <t>-0.00474371219356895 +/- 0.001069741968571244</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.0035316576519249356 +/- 0.001227730281996473</t>
+          <t>0.0011135857461024967 +/- 0.0007954183900731948</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3111,157 +3111,157 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.00426344257079222 +/- 0.0017840083702037781</t>
+          <t>-0.00019090041361752297 +/- 0.0011311733270525808</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-0.0031498568246897786 +/- 0.0008471859341835421</t>
+          <t>0.00279987273305764 +/- 0.0009416893787431378</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.0022589882278078012 +/- 0.0013153055430222408</t>
+          <t>-0.0012726694241170454 +/- 0.001485538342975357</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.0002545338848234047 +/- 0.0010723703179352571</t>
+          <t>-0.0017181037225580177 +/- 0.0012256672150339357</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.001368119630925857 +/- 0.0010841059521095036</t>
+          <t>-0.0005090677696467871 +/- 0.001076139645261705</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0002012267044332573</t>
+          <t>-3.181673560290754e-05 +/- 0.0002642896551994139</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.0009863188036907556 +/- 0.0012682870778233952</t>
+          <t>0.0036589245943366767 +/- 0.0015275346973156495</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.0023544384346166013 +/- 0.0019047571806676152</t>
+          <t>0.011294941139039205 +/- 0.0023692254777132092</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.007158765510658627 +/- 0.003072416149511297</t>
+          <t>0.014412981228126055 +/- 0.0027555938176486924</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.00025453388482343797 +/- 0.0010533213717624256</t>
+          <t>0.00337257397391032 +/- 0.0014869005975880246</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-3.181673560290754e-05 +/- 0.0016126409032738438</t>
+          <t>0.0030225898822781373 +/- 0.0009027210282603251</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-0.002736239261851736 +/- 0.001217379985345776</t>
+          <t>0.0008590518612790921 +/- 0.0015590200445434368</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.0010181355392936964 +/- 0.00231104292680051</t>
+          <t>0.009640470887686969 +/- 0.0025534788707901124</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.001272669424117101 +/- 0.0020815052158824035</t>
+          <t>0.006426980591791342 +/- 0.0014635698377346317</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.002895322939866385 +/- 0.0015873330809120518</t>
+          <t>0.0018135539293668956 +/- 0.0013502446817641165</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.0021635380209990562 +/- 0.0008863116943801588</t>
+          <t>0.0017181037225581287 +/- 0.0010947916343675079</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>-0.00028635062042633443 +/- 0.0017568485768092183</t>
+          <t>-0.0035316576519248575 +/- 0.0009049610342556767</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>-0.0009226853324848627 +/- 0.0006275241146457544</t>
+          <t>0.0014635698377346907 +/- 0.0013736578520472684</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.0007954183900731992 +/- 0.00021343315089081638</t>
+          <t>0.00012726694241174119 +/- 0.0003542961732631269</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.007158765510658615 +/- 0.0012746564189634072</t>
+          <t>0.0132039452752148 +/- 0.0017266259689742564</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>-0.005758829144129807 +/- 0.0012027399409122392</t>
+          <t>-0.0058860960865414706 +/- 0.0012177956862236467</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.001718103722558062 +/- 0.0013883184364792455</t>
+          <t>0.002354438434616657 +/- 0.0010947916343675222</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>-0.0013999363665287757 +/- 0.0005547437408260542</t>
+          <t>0.0008590518612790699 +/- 0.0009004754500849521</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.0003181673560292642 +/- 0.0008049068177329458</t>
+          <t>0.0015908367801464097 +/- 0.0011293820775882168</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.0009545020680877814 +/- 0.0004499565900009823</t>
+          <t>-0.0008272351256760513 +/- 0.00038180082723513473</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>-0.005790645879732737 +/- 0.001504497666883459</t>
+          <t>0.0008590518612790809 +/- 0.0014161128275067033</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-0.005854279350938574 +/- 0.0016483402923307224</t>
+          <t>-0.005567928730512173 +/- 0.00125867263409815</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>-0.0029271396754692704 +/- 0.0011185743449727578</t>
+          <t>-0.0061088132357619675 +/- 0.0016085554769028996</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-0.0024817053770283095 +/- 0.0010041192388202023</t>
+          <t>-0.00649061406299708 +/- 0.0013438569571710209</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-0.00038180082723511256 +/- 0.000342676729693558</t>
+          <t>-0.000986318803690689 +/- 0.0004599692107795414</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3.181673560295195e-05 +/- 0.0004814745768508303</t>
+          <t>0.0003499840916322383 +/- 0.0003613686507031764</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -3271,122 +3271,122 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.003913458479160037 +/- 0.0010265520715813956</t>
+          <t>-0.005408845052497569 +/- 0.001138310138084535</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.0014317531021317165 +/- 0.0017383122341263272</t>
+          <t>-0.00467706013363024 +/- 0.0005875337356862633</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>0.0013363028953229383 +/- 0.0008513578212064718</t>
+          <t>-0.0011454024817053377 +/- 0.0007420874190067006</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.0012090359529112415 +/- 0.000371043709503356</t>
+          <t>0.0017181037225581174 +/- 0.00047618929516688433</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-0.0018453706649697477 +/- 0.0011275879826070292</t>
+          <t>0.0034680241807191316 +/- 0.0015616151691769538</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>-0.006776964683423481 +/- 0.0009116480293919376</t>
+          <t>-0.0020680878141902115 +/- 0.00135921154077593</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>0.0002863506204263677 +/- 0.0005020596194101008</t>
+          <t>0.0005090677696468982 +/- 0.0005361851589676365</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.001495386573337587 +/- 0.0012408526885141435</t>
+          <t>0.0002545338848234602 +/- 0.0008976605777706698</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.006872414890232237 +/- 0.0014454746028126795</t>
+          <t>-0.008749602290804936 +/- 0.0014246651719527776</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>-0.0038498250079541663 +/- 0.00079795966935948</t>
+          <t>0.0006363347120585949 +/- 0.0009960213708239598</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-0.006872414890232248 +/- 0.001513888291870227</t>
+          <t>-0.00830416799236392 +/- 0.0016375576496923706</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>-0.003118040089086849 +/- 0.0015959193387189803</t>
+          <t>-0.00031816735602923084 +/- 0.0016160897358193415</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.0020680878141902783 +/- 0.0010952538643371683</t>
+          <t>0.00776328348711427 +/- 0.0009775559335499175</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>0.0013363028953229605 +/- 0.0011454024817053648</t>
+          <t>0.0009863188036907666 +/- 0.0013075865471227877</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-0.0012090359529112083 +/- 0.0006169493932442013</t>
+          <t>3.181673560296305e-05 +/- 0.0005218332633425621</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>-0.004008908685968826 +/- 0.0011131311285100833</t>
+          <t>-0.0006045179764555542 +/- 0.0009049610342556802</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>-0.0015272033089404834 +/- 0.000983749591711123</t>
+          <t>-0.0025135221126311945 +/- 0.0016063513282041715</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-0.0021953547566019526 +/- 0.001649874917271937</t>
+          <t>-0.006331530384982453 +/- 0.001593697713823514</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-0.0017499204581609806 +/- 0.001388682968042972</t>
+          <t>-0.0008908685968819108 +/- 0.0014566367346178274</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>0.00038180082723513473 +/- 0.00039739090031170265</t>
+          <t>-0.00038180082723506816 +/- 0.00023809464758343547</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.00069996818326441 +/- 0.0004887779667749406</t>
+          <t>-0.0023226216990136273 +/- 0.0006831342842374736</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.00044543429844100534 +/- 0.0002916051985336246</t>
+          <t>0.0001272669424117301 +/- 0.0002545338848234185</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-0.0004136175628380423 +/- 0.001444423730552496</t>
+          <t>-0.0004136175628379979 +/- 0.0016958648388465177</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-0.0057588291441297845 +/- 0.0017797475368688646</t>
+          <t>-0.002449888641425324 +/- 0.0009965294154225782</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3396,92 +3396,92 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>0.0001272669424117301 +/- 0.0004315831996898196</t>
+          <t>0.0003181673560293197 +/- 0.00044995659000099023</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>-0.00426344257079223 +/- 0.001424309849544984</t>
+          <t>-0.0012090359529111638 +/- 0.0012306127652442855</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-0.009449570474069325 +/- 0.0013577211767961655</t>
+          <t>-0.013713013044861555 +/- 0.0016000370296761078</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>-0.0002545338848234047 +/- 0.000648936622792603</t>
+          <t>0.0003181673560293086 +/- 0.0006363347120585451</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-0.0019090041361756183 +/- 0.00131183761553221</t>
+          <t>-0.003690741329939484 +/- 0.0010947916343675079</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-0.00429525930639515 +/- 0.0016910826937217086</t>
+          <t>0.00022271714922054154 +/- 0.002110723295020301</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-0.00025453388482341575 +/- 0.0014704702524074172</t>
+          <t>0.0041043588927776485 +/- 0.0020044543429844196</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-0.0011772192173082896 +/- 0.0011737745304293199</t>
+          <t>-0.0005727012408526466 +/- 0.0011454024817054073</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>0.00015908367801465985 +/- 0.0003557219181514185</t>
+          <t>0.00022271714922053042 +/- 0.00031975423547949517</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>9.545020680878924e-05 +/- 0.0013945025135737225</t>
+          <t>0.0003181673560293086 +/- 0.0012404447145795596</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.0020999045497931855 +/- 0.0010761396452617273</t>
+          <t>-0.00155902004454338 +/- 0.0005771033136244696</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-0.00019090041361754517 +/- 0.0006853534593871605</t>
+          <t>0.00044543429844101645 +/- 0.00043158319968983924</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-0.0020999045497931633 +/- 0.0017783249904526801</t>
+          <t>0.001654470251352258 +/- 0.0021849551019267484</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>0.00022271714922051934 +/- 0.0008423927645481161</t>
+          <t>0.000190900413617634 +/- 0.0010475391430578955</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>-0.003118040089086849 +/- 0.0019132416644445393</t>
+          <t>-0.005631562201718043 +/- 0.0016038285919349141</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>-0.00019090041361755628 +/- 0.0002545338848233991</t>
+          <t>-0.00012726694241165236 +/- 0.00025453388482338804</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>0.0005727012408527022 +/- 0.000547395817183752</t>
+          <t>-0.00022271714922045271 +/- 0.0003499840916321818</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>0.0005090677696468537 +/- 0.00038180082723513105</t>
+          <t>-0.0007954183900731216 +/- 0.0007149922066256386</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3491,52 +3491,52 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>0.00025453388482342686 +/- 0.0008748155956008585</t>
+          <t>-0.0010817690104994782 +/- 0.0004969932978623212</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>0.0010499522748965927 +/- 0.0010747276967263439</t>
+          <t>0.002131721285396182 +/- 0.00137990763233863</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>6.363347120585949e-05 +/- 0.00012726694241171899</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>-0.0007317849188673287 +/- 0.0005875337356862705</t>
+          <t>-0.0007954183900731326 +/- 0.000326024523256775</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>0.002418071905822483 +/- 0.0013588391030265863</t>
+          <t>0.001431753102131772 +/- 0.0012260801061405146</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>-0.0010817690104995004 +/- 0.0008074182335634269</t>
+          <t>0.004040725421571823 +/- 0.0013122233934013013</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>6.363347120585949e-05 +/- 0.00027737187041304687</t>
+          <t>-0.00015908367801459322 +/- 0.000555655399190993</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>-0.001018135539293652 +/- 0.0007085923465262538</t>
+          <t>-9.545020680873373e-05 +/- 0.001539417168743601</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>-0.0024498886414253684 +/- 0.0009226853324848861</t>
+          <t>-0.0013999363665287423 +/- 0.0016544702513522059</t>
         </is>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>-0.0004772510340438796 +/- 0.0005735843581711762</t>
+          <t>0.0004772510340439573 +/- 0.000978073569770251</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.0036087369420702677 +/- 0.0018469075208375919</t>
+          <t>-0.00034821145932257825 +/- 0.0014468369587877644</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3556,157 +3556,157 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.02222222222222222 +/- 0.002338231758482969</t>
+          <t>-0.017125672681228242 +/- 0.002604429651418391</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0013611902500791472 +/- 0.001551123773345993</t>
+          <t>0.00705919594808484 +/- 0.0012099724503713896</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.008515352959797407 +/- 0.0023238305985733097</t>
+          <t>-0.0009813232035454367 +/- 0.0018264478299147328</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.0006331117442228473 +/- 0.0018834409345544342</t>
+          <t>0.006900918012029122 +/- 0.0019707986598636778</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.010889522000633112 +/- 0.002611154242140079</t>
+          <t>-0.008040519151630265 +/- 0.0028707272044962828</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.00018993352326686087 +/- 0.000290128249126682</t>
+          <t>0.00015827793605571738 +/- 0.00029185009361484945</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.013263691041468805 +/- 0.0016717627004129104</t>
+          <t>-0.005824628046850277 +/- 0.001957534008704055</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.023361823361823374 +/- 0.0036253594940729088</t>
+          <t>0.031623931623931636 +/- 0.002653976944441044</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.04070908515352959 +/- 0.003086054474695524</t>
+          <t>0.03143399810066476 +/- 0.0041829717376016175</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-0.00031655587211142365 +/- 0.002242860346175168</t>
+          <t>-0.004178537511870861 +/- 0.0017895908863694273</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-0.005792972459639123 +/- 0.0015446499396968448</t>
+          <t>-0.012757201646090543 +/- 0.0018076975669856512</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-0.002089268755935403 +/- 0.001962646407090854</t>
+          <t>-0.002405824628046849 +/- 0.001652166932662211</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.009433364988920546 +/- 0.002722380500158267</t>
+          <t>0.019025007913896785 +/- 0.0021209243431465747</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.019816397594175382 +/- 0.0014725803544935873</t>
+          <t>0.026970560303893644 +/- 0.001934878985746901</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>-0.010572966128521688 +/- 0.0017058807958603816</t>
+          <t>-0.007502374169040838 +/- 0.0020172831866229358</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0.01076289965178855 +/- 0.0012819535758984983</t>
+          <t>0.0011079455523899996 +/- 0.0013523272784611495</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>-0.00034821145932256714 +/- 0.001118746251793118</t>
+          <t>-0.005729661285216847 +/- 0.0014674678045583248</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>0.001139601139601132 +/- 0.002157230140854812</t>
+          <t>-0.0014561570117125888 +/- 0.000863449300220691</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.00018993352326686087 +/- 0.000290128249126682</t>
+          <t>0.0005064893953782956 +/- 0.0002901282491266821</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.0057613168724279795 +/- 0.0023467873368598416</t>
+          <t>-0.011079455523899972 +/- 0.0020854281851219385</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>-0.0028490028490028574 +/- 0.0024561145604648105</t>
+          <t>-0.010066476733143403 +/- 0.001341539734119504</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>-0.0031339031339031485 +/- 0.0017650651294017843</t>
+          <t>0.00015827793605570627 +/- 0.0014864649423075706</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>-0.0012978790756568604 +/- 0.001188244658380711</t>
+          <t>-0.001804368471035145 +/- 0.0009710580341992875</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.0033871478315922743 +/- 0.0015052223397238119</t>
+          <t>-0.003925292814181714 +/- 0.0023010803223027726</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.0048433048433048406 +/- 0.0006178924120273369</t>
+          <t>-0.00037986704653372174 +/- 0.0005446233154189819</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>-0.005698005698005692 +/- 0.0028454833876852496</t>
+          <t>-0.012598923710034838 +/- 0.0013189405923393165</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-0.009085153529597979 +/- 0.0016872754632778104</t>
+          <t>-0.016587527698638825 +/- 0.0014861278372023448</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>-0.0072491294713516894 +/- 0.0016837082807182222</t>
+          <t>-0.007913896802785703 +/- 0.0015827793605571294</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-0.01497309275087052 +/- 0.0025680076875412594</t>
+          <t>-0.0012345679012345622 +/- 0.001979170501087763</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-0.0010762899651788782 +/- 0.0006203202894037944</t>
+          <t>-0.0005698005698005826 +/- 0.00027596701130362596</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.0005064893953782956 +/- 0.0005143424124492652</t>
+          <t>-0.00047483380816715215 +/- 0.0006211274729455215</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -3716,122 +3716,122 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.011839189616967394 +/- 0.0014995529322351273</t>
+          <t>-0.012282367837923424 +/- 0.0010479864107152087</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.012503956948401396 +/- 0.0018308317494043947</t>
+          <t>-0.008958531180753427 +/- 0.002579687588715345</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>0.0010762899651788672 +/- 0.0011431130158447498</t>
+          <t>-0.0005698005698005826 +/- 0.0008230452674897303</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.0002849002849002913 +/- 0.0008187728494066383</t>
+          <t>-0.000664767331434013 +/- 0.0009648465118156702</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-0.0013928458372902796 +/- 0.0017749725569960336</t>
+          <t>-0.008293763849319402 +/- 0.0012803892634477025</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>-0.011934156378600824 +/- 0.001608215991881035</t>
+          <t>-0.009465020576131699 +/- 0.0012854663187240834</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>0.0015194681861348757 +/- 0.0006456498276154123</t>
+          <t>0.001551123773345997 +/- 0.001015448871943341</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.002943969610636266 +/- 0.0020023253688975597</t>
+          <t>0.001899335232668542 +/- 0.0014297676214797214</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.009465020576131689 +/- 0.0014188626040528703</t>
+          <t>-0.007660652105096544 +/- 0.0014492590240278002</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.011490978157644827 +/- 0.0020321309079713652</t>
+          <t>-0.008768597657486565 +/- 0.002282936338347934</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.004906616017727128 +/- 0.0012442699592930667</t>
+          <t>-0.004558404558404572 +/- 0.0016215572617747091</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.00816714150047484 +/- 0.00156238843675251</t>
+          <t>0.0004748338081671299 +/- 0.0014864649423075502</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.0008547008547008627 +/- 0.002161174952668345</t>
+          <t>0.0015194681861348646 +/- 0.0013563966625912277</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-0.003861981639759415 +/- 0.0021646496989273637</t>
+          <t>-0.010826210826210835 +/- 0.001510207083491818</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>3.1655587211143474e-05 +/- 0.0003304940332038868</t>
+          <t>-0.0008547008547008739 +/- 0.0006942612282197468</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>0.0001266223488445628 +/- 0.00129903669064155</t>
+          <t>0.004051915163026265 +/- 0.0017210860676249806</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.004779993668882576 +/- 0.0015919330117986881</t>
+          <t>0.0013295346628679817 +/- 0.002471569648109302</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-0.014656536878759096 +/- 0.0019872549687520785</t>
+          <t>-0.008926875593542249 +/- 0.0012881918296534316</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.0024691358024691466 +/- 0.001523419995633546</t>
+          <t>-0.010699588477366273 +/- 0.0017613710342821865</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-0.0005698005698005826 +/- 0.0008703847473800462</t>
+          <t>-0.0014245014245014564 +/- 0.0005706792142234996</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>-0.001677746122190593 +/- 0.0006647673314339936</t>
+          <t>-0.0015511237733460304 +/- 0.00026295105612276863</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>-0.0027540360873694048 +/- 0.0004914268659784424</t>
+          <t>-0.001519468186134887 +/- 0.0005627220270538644</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-0.005318138651472004 +/- 0.001594134639064801</t>
+          <t>-0.004653371320037991 +/- 0.0018943164672842157</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.003956948401392835 +/- 0.0019629016774837167</t>
+          <t>-0.00807217473884142 +/- 0.0016943872986479984</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3841,92 +3841,92 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>0.00031655587211143477 +/- 0.000721858452104567</t>
+          <t>0.0009180120291231609 +/- 0.00047903595917764784</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>0.0009813232035454477 +/- 0.0012776471079842368</t>
+          <t>-0.0020576131687242926 +/- 0.0011347545634020045</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-0.008483697372586262 +/- 0.001783982627870259</t>
+          <t>-0.007977207977207978 +/- 0.00138563270834055</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>-0.0036720481164925324 +/- 0.0009086862991077965</t>
+          <t>-0.0016144349477683062 +/- 0.0007141826003594981</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.0013295346628680038 +/- 0.0012079002233832796</t>
+          <t>-0.00538144982589428 +/- 0.000825476721139955</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-0.007344096232985131 +/- 0.0021036084489820988</t>
+          <t>-0.000538144982589428 +/- 0.0021425478010785055</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-0.010921177587844255 +/- 0.0016156758664355583</t>
+          <t>-0.006457739791073125 +/- 0.001590358554869314</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>0.001804368471035156 +/- 0.0013284036250938392</t>
+          <t>0.0063944286166508265 +/- 0.0014492590240277943</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>0.0009496676163343043 +/- 0.00031655587211143477</t>
+          <t>0.0005698005698005826 +/- 0.0006456498276154352</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>-0.0003798670465336995 +/- 0.0018228781321795516</t>
+          <t>0.0021209243431465573 +/- 0.0007497764661175418</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>-0.0006014561570117149 +/- 0.0014878125989237242</t>
+          <t>-0.0030072807850585635 +/- 0.0008869215401153228</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-0.0033554922443810977 +/- 0.000452132220863755</t>
+          <t>3.1655587211143474e-05 +/- 0.0007939180882548106</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>0.00015827793605571738 +/- 0.0012916876076672125</t>
+          <t>0.004178537511870839 +/- 0.001463022476516805</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>-0.0015194681861348536 +/- 0.0013189405923393117</t>
+          <t>-0.004273504273504281 +/- 0.0016884628493946995</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>0.007217473884140568 +/- 0.0021553712605950274</t>
+          <t>-0.008072174738841397 +/- 0.0008405139631118344</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>-0.0008863564419120063 +/- 0.0006299382317863859</t>
+          <t>-0.00031655587211143477 +/- 0.0002831361794871592</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>-0.00047483380816715215 +/- 0.0004066233801413554</t>
+          <t>6.331117442228695e-05 +/- 0.00041995882119094327</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>-0.0025641025641025663 +/- 0.0007280785058562493</t>
+          <t>-0.0010762899651788782 +/- 0.000636269428371074</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>-0.00018993352326686087 +/- 0.0004293972765511504</t>
+          <t>-0.001139601139601154 +/- 0.0007907563150868438</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>-0.004178537511870839 +/- 0.0012079002233832893</t>
+          <t>0.0002532446976891256 +/- 0.0012486915431032548</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -3951,37 +3951,37 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>0.00018993352326686087 +/- 0.0009411882714351908</t>
+          <t>-3.1655587211143474e-05 +/- 0.001015448871943387</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>-0.005571383349161141 +/- 0.00128351598181157</t>
+          <t>-0.003925292814181714 +/- 0.0016762522690565037</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>-0.004273504273504281 +/- 0.0015263771384920787</t>
+          <t>-0.0024691358024691358 +/- 0.0011995755189297913</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>0.00015827793605571738 +/- 0.0009310187508612264</t>
+          <t>-0.00018993352326686087 +/- 0.00047377744688496684</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>-0.0014561570117125667 +/- 0.0014311686679907864</t>
+          <t>-0.0013295346628680149 +/- 0.0010855605064566214</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>-0.006267806267806287 +/- 0.0010188969255733595</t>
+          <t>-0.0004115226337448763 +/- 0.0017909902070042177</t>
         </is>
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>-0.0026907249129471066 +/- 0.0008163214281878635</t>
+          <t>-0.006172839506172867 +/- 0.0009627670988126552</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.004183673469387794 +/- 0.002322160433836501</t>
+          <t>-0.0007482993197278853 +/- 0.0015347638330174714</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4001,157 +4001,157 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.004081632653061285 +/- 0.0014024168794617774</t>
+          <t>0.002857142857142847 +/- 0.0023129251700680195</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0012925170068027515 +/- 0.002123059392425455</t>
+          <t>-0.0022789115646258407 +/- 0.0021244212883846517</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.0001700680272109345 +/- 0.0015899314139483423</t>
+          <t>0.0005442176870748327 +/- 0.0015452811825306862</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.006972789115646227 +/- 0.001530612244897964</t>
+          <t>-0.00748299319727892 +/- 0.0016241273994984098</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.004659863945578191 +/- 0.0021514781769889028</t>
+          <t>-0.019897959183673476 +/- 0.0023281312868908255</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.00023809523809521506 +/- 0.0003741496598639498</t>
+          <t>-3.401360544218468e-05 +/- 0.0005578646077162146</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.00040816326530618285 +/- 0.0020283063286905575</t>
+          <t>-0.000850340136054406 +/- 0.0017293501794402905</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.00833333333333336 +/- 0.0031844074390879047</t>
+          <t>0.014183673469387759 +/- 0.0032944068900041634</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.00806122448979596 +/- 0.0032413020763813567</t>
+          <t>0.017755102040816317 +/- 0.003314538153763201</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.005136054421768743 +/- 0.0018218723456927834</t>
+          <t>-0.013979591836734685 +/- 0.002032010480441349</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>6.802721088440266e-05 +/- 0.002117603049833113</t>
+          <t>-0.004693877551020398 +/- 0.0014171882078911346</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-0.00343537414965982 +/- 0.0015620357147217922</t>
+          <t>-0.008741496598639464 +/- 0.0021298601638711965</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-0.020884353741496574 +/- 0.0017088240390585787</t>
+          <t>-0.019693877551020412 +/- 0.002082621702699542</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.020340136054421788 +/- 0.0017128814029951024</t>
+          <t>0.021394557823129257 +/- 0.0018091273669350095</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.0006122448979592243 +/- 0.0011464149351260355</t>
+          <t>-0.0030272108843537593 +/- 0.0009793319761148248</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.002210884353741538 +/- 0.001883076263355967</t>
+          <t>-0.008911564625850344 +/- 0.0017061137692496026</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>-0.022380952380952356 +/- 0.0025670696957977137</t>
+          <t>-0.019285714285714285 +/- 0.0019363871193864416</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>-0.0031632653061224093 +/- 0.001602975737135816</t>
+          <t>-0.0037755102040816337 +/- 0.0017105157769632773</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-0.00010204081632649852 +/- 0.00026565475088119</t>
+          <t>-6.802721088435825e-05 +/- 0.00029652373765582236</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.005748299319727934 +/- 0.0018719847490907594</t>
+          <t>0.0017687074829932149 +/- 0.0029993751952446966</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>-0.004727891156462549 +/- 0.0011629470066175933</t>
+          <t>-0.0028231292517006843 +/- 0.00119822550706182</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>-0.0015986394557822802 +/- 0.001245566899564656</t>
+          <t>-0.002585034013605425 +/- 0.0011899901826214838</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>-3.401360544212917e-05 +/- 0.0013125021348010146</t>
+          <t>-0.003061224489795911 +/- 0.001551259081767533</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.0021088435374149285 +/- 0.0010181380644282813</t>
+          <t>-0.0052721088435374154 +/- 0.0009407698425809001</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.0015986394557822802 +/- 0.0005901139990781157</t>
+          <t>0.0005102040816326481 +/- 0.0006673951316444902</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>-0.0005442176870747884 +/- 0.0019610252116189853</t>
+          <t>0.0027551020408163153 +/- 0.0013978722849003092</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0.014455782312925214 +/- 0.00230816837786714</t>
+          <t>0.005714285714285727 +/- 0.0017463262112916195</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>0.0008843537414966352 +/- 0.0014841785189980536</t>
+          <t>0.0016326530612244983 +/- 0.0013243484580906005</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.007278911564625878 +/- 0.0011198692267451803</t>
+          <t>-0.008197278911564609 +/- 0.0023291249409210938</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>-0.0005102040816326259 +/- 0.0005102040816326629</t>
+          <t>-0.0008503401360544394 +/- 0.00046263505131754036</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.001156462585033957 +/- 0.0005930474753116498</t>
+          <t>0.0007142857142857006 +/- 0.0007366125111465189</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -4161,122 +4161,122 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.0007823129251701144 +/- 0.0018129602681954441</t>
+          <t>-0.0035034013605442227 +/- 0.0016804924254470268</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.01119047619047624 +/- 0.0026013182047617627</t>
+          <t>0.005544217687074837 +/- 0.0024950782224616814</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>0.0008503401360544615 +/- 0.0007940556142808738</t>
+          <t>-0.0004421768707483009 +/- 0.00030612244897960906</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-0.0010884353741496323 +/- 0.00045124146807555944</t>
+          <t>0.0004761904761904745 +/- 0.0007933267884143326</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-0.005442176870748261 +/- 0.0012996580390845492</t>
+          <t>-0.005510204081632664 +/- 0.002005360948705279</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>0.0034353741496599088 +/- 0.001025497512359273</t>
+          <t>-0.0009863945578231336 +/- 0.00217500983384327</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>0.0006802721088436048 +/- 0.000504503298441893</t>
+          <t>0.00027210884353741084 +/- 0.0005650764532597411</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.0030612244897958774 +/- 0.0009974747141915069</t>
+          <t>-0.0035034013605442006 +/- 0.0015811754148529929</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.0026870748299320014 +/- 0.0012767567604845857</t>
+          <t>0.0019387755102040715 +/- 0.001761169179047561</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>-0.0007482993197278631 +/- 0.000757518960929267</t>
+          <t>-0.000952380952380949 +/- 0.0015939285052870616</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-0.00812925170068024 +/- 0.0020433657545408995</t>
+          <t>-0.015918367346938765 +/- 0.0017660891137071207</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>-0.00037414965986390933 +/- 0.0011428773888715119</t>
+          <t>-0.005510204081632641 +/- 0.0009101420517183535</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-0.0017346938775509746 +/- 0.0015620357147217814</t>
+          <t>-0.006768707482993186 +/- 0.0012857862701656931</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.01180272108843533 +/- 0.0015215149147173432</t>
+          <t>-0.011802721088435376 +/- 0.001207842238405773</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>0.00040816326530616063 +/- 0.0007874718981490127</t>
+          <t>0.0011904761904761641 +/- 0.0011306646352785457</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>0.00010204081632656515 +/- 0.0014907895918919152</t>
+          <t>-0.012687074829931966 +/- 0.0015215149147173388</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>-0.02265306122448977 +/- 0.001395801668617907</t>
+          <t>-0.02282312925170068 +/- 0.0022171548962900884</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-0.018639455782312873 +/- 0.001976304632154263</t>
+          <t>-0.032517006802721085 +/- 0.00046138299204933584</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-0.014795918367346905 +/- 0.0016330073311779155</t>
+          <t>-0.036292517006802714 +/- 0.0021622061326956213</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>0.000646258503401409 +/- 0.0004917289896190941</t>
+          <t>-0.000340136054421758 +/- 0.0005484529080475293</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>3.401360544220688e-05 +/- 0.0009308797403676256</t>
+          <t>0.0014965986394557928 +/- 0.0007933267884143183</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.00040816326530616063 +/- 0.0004998958658741345</t>
+          <t>0.0003061224489795955 +/- 0.00028253822662988325</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-0.014387755102040777 +/- 0.0020125594819710236</t>
+          <t>-0.03561224489795918 +/- 0.0025726970200477283</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-0.01258503401360539 +/- 0.0020967394567921764</t>
+          <t>-0.026020408163265306 +/- 0.0016955705551856615</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4286,92 +4286,92 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>3.401360544220688e-05 +/- 0.0013558592808159654</t>
+          <t>-0.00013605442176870542 +/- 0.0010112971936951378</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>-0.003809523809523785 +/- 0.0014007660055764504</t>
+          <t>-0.01411564625850339 +/- 0.0012839854481753086</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>-0.008333333333333293 +/- 0.0014208570458643084</t>
+          <t>-0.0085374149659864 +/- 0.0012585034013605438</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>-0.0014285714285713791 +/- 0.000947509406611178</t>
+          <t>0.00010204081632652074 +/- 0.001054421768707474</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-0.004319727891156433 +/- 0.0014514685913844822</t>
+          <t>-0.0058843537414966065 +/- 0.0020524047403463357</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-0.016360544217687047 +/- 0.0012399813696297858</t>
+          <t>-0.03023809523809524 +/- 0.0013643653823218725</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-0.0013945578231292055 +/- 0.0014704738994025307</t>
+          <t>-0.013537414965986394 +/- 0.0017196224026890699</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-0.0015306122448979441 +/- 0.00117087853592235</t>
+          <t>-0.0009183673469387643 +/- 0.0018508527701241939</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>0.0018707482993197688 +/- 0.0003485357403387281</t>
+          <t>0.001054421768707492 +/- 0.0002825382266298392</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0.008741496598639487 +/- 0.0020524047403463457</t>
+          <t>0.00921768707482994 +/- 0.0016130483947454704</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>-0.005102040816326503 +/- 0.0012726725805353467</t>
+          <t>-0.007006802721088457 +/- 0.0014446775905846952</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.0026870748299320122 +/- 0.0011224489795918112</t>
+          <t>0.0006802721088435271 +/- 0.001031683733884549</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>0.009557823129251741 +/- 0.0020205913932352534</t>
+          <t>0.009591836734693871 +/- 0.002305911735602497</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>0.010476190476190528 +/- 0.0017595261437248402</t>
+          <t>0.000510204081632637 +/- 0.0013962160375356253</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>0.011666666666666704 +/- 0.0016244835287427936</t>
+          <t>-0.0025510204081632625 +/- 0.0019195851781663184</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>-0.0002721088435373997 +/- 0.000333263910582738</t>
+          <t>-3.4013605442173576e-05 +/- 0.0005367256407503133</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>-0.0012585034013605112 +/- 0.0007303030800538619</t>
+          <t>-0.00020408163265306367 +/- 0.0008219759165710615</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>0.002040816326530648 +/- 0.0010863074437191325</t>
+          <t>0.0015646258503401512 +/- 0.0012092781520157217</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4381,52 +4381,52 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>0.0020068027210884743 +/- 0.0006533800242278253</t>
+          <t>0.0017687074829931815 +/- 0.000726331853879695</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>0.0011904761904762307 +/- 0.0012749431846252454</t>
+          <t>0.0025850340136054474 +/- 0.0013190965598411796</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.0007482993197279186 +/- 0.000254534516107064</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>-0.0001360544217686721 +/- 0.0005090690322141503</t>
+          <t>0.0020748299319727883 +/- 0.0011428773888715322</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>-0.005986394557823083 +/- 0.001011297193695129</t>
+          <t>0.0008843537414965797 +/- 0.0012188076780387028</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>0.00459183673469391 +/- 0.0018078479273358054</t>
+          <t>-0.011428571428571444 +/- 0.0015377761299942016</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>0.002721088435374208 +/- 0.0011383129612708438</t>
+          <t>0.0009183673469387643 +/- 0.0012455668995646706</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>0.000816326530612288 +/- 0.0017489741676438722</t>
+          <t>0.0022108843537414825 +/- 0.002709371030071765</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>0.014625850340136092 +/- 0.002845782403177125</t>
+          <t>0.010544217687074853 +/- 0.0024338154857140647</t>
         </is>
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>-0.004693877551020376 +/- 0.000922765984098679</t>
+          <t>-0.006734693877551023 +/- 0.0011958092402208876</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.0013221541438246053 +/- 0.00116672379975012</t>
+          <t>-0.003418252176717218 +/- 0.0009143790312001111</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4446,157 +4446,157 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.0040954530796516895 +/- 0.001337792229132007</t>
+          <t>0.00016123831022246682 +/- 0.0012173225468027449</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.00035472428248956023 +/- 0.0013408979610636323</t>
+          <t>0.0038052241212511717 +/- 0.001280195629879345</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.0005804579168010027 +/- 0.0012389147186261512</t>
+          <t>-0.0015478877781361256 +/- 0.0014622101320547719</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.003869719445340247 +/- 0.0025227484315521282</t>
+          <t>0.0015156401160915545 +/- 0.0018301791194663321</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0003224766204449669 +/- 0.0015398047579894558</t>
+          <t>0.00038697194453399806 +/- 0.0012720466251735546</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0003224766204449669 +/- 0.00024978931610493866</t>
+          <t>-0.0006449532408900783 +/- 0.000576863715575565</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.003708481135117736 +/- 0.0016709766408296088</t>
+          <t>-0.002547565301515675 +/- 0.0011025682681250497</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-0.022573363431151284 +/- 0.0020598154689030986</t>
+          <t>-0.005320864237342815 +/- 0.0021158496874974803</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.03253789100290233 +/- 0.003683722012996197</t>
+          <t>-0.0118671396323767 +/- 0.002381965212849964</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-0.000193485972267049 +/- 0.0012506107339352005</t>
+          <t>0.0001612383102224557 +/- 0.0023487723617710518</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-0.0016123831022251233 +/- 0.0011263624119040897</t>
+          <t>-3.3306690738754695e-17 +/- 0.0019132404997344549</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.0002579812963559691 +/- 0.0016805951913312258</t>
+          <t>-0.0006772009029345716 +/- 0.002131519235041692</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.014575943244114754 +/- 0.0033475496349205927</t>
+          <t>0.008868107062237961 +/- 0.0020711435953990848</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.02292808771364071 +/- 0.0031905635400530773</t>
+          <t>0.012641083521444652 +/- 0.0024295141182634613</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>-0.0019026120606256524 +/- 0.0012275308810496097</t>
+          <t>-0.0027088036117381862 +/- 0.0017317925291322111</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-0.003192518542405709 +/- 0.0017806433656599107</t>
+          <t>-0.0028700419219607086 +/- 0.0009722549778575675</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>9.6742986133469e-05 +/- 0.0009126715058422975</t>
+          <t>-0.003063527894227691 +/- 0.0010816194667041766</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>-0.006514027732989392 +/- 0.0016743959994514343</t>
+          <t>0.0023863269912931086 +/- 0.0009587919217877119</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-0.000193485972267049 +/- 0.0005981050303447677</t>
+          <t>-0.0009029345372460918 +/- 0.00040277316984187596</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.004095453079651701 +/- 0.0012326033443158047</t>
+          <t>0.003966462431473694 +/- 0.002149010910228457</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>-0.0031280232183167 +/- 0.0021000632254324155</t>
+          <t>-0.007836181876813952 +/- 0.0011360151534220283</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>-0.0037407287971622403 +/- 0.0009368486969580196</t>
+          <t>0.0013221541438245277 +/- 0.0011396708833971312</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.00032247662044497804 +/- 0.0006608804105746176</t>
+          <t>0.0011609158336020164 +/- 0.0009695773220492214</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-9.67429861335467e-05 +/- 0.0014990827860908388</t>
+          <t>0.0056755885198322975 +/- 0.0009802440602109381</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.00016123831022254453 +/- 0.00038831327245379417</t>
+          <t>-0.0003224766204450669 +/- 0.0004995786322099202</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>-0.0005159625927120715 +/- 0.0011822188184342631</t>
+          <t>0.006900999677523345 +/- 0.0015545915244364896</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-0.006030312802321858 +/- 0.0014497108541108618</t>
+          <t>-0.006643018381167387 +/- 0.0008055463396837571</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>-0.010287004192196103 +/- 0.001893846741054625</t>
+          <t>-0.013415027410512769 +/- 0.0013075224077854256</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>-0.003289261528539189 +/- 0.0007739438890680554</t>
+          <t>-0.004095453079651768 +/- 0.0011541780179408758</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>-0.0005482102547565759 +/- 0.0006772009029345303</t>
+          <t>-0.00045146726862306253 +/- 0.00032886291606534735</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.0009674298613349897 +/- 0.0004995786322099202</t>
+          <t>-0.0007094485649790649 +/- 0.0007035609232270652</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -4606,122 +4606,122 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.006159303450499876 +/- 0.001014136420091369</t>
+          <t>-0.004933892292808795 +/- 0.0016759479471378544</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.0032247662044502024 +/- 0.001491781168167746</t>
+          <t>0.0007416962270235028 +/- 0.0010700199950362682</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>-0.00045146726862306253 +/- 0.0006640200026434822</t>
+          <t>-0.0013221541438246276 +/- 0.0006360233125867844</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-0.0012576588197356076 +/- 0.0007692267295631413</t>
+          <t>0.00032247662044497804 +/- 0.0006764326657014932</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>0.002515317639471093 +/- 0.0009970735139465052</t>
+          <t>0.0042244437278297076 +/- 0.002449336775460605</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>-0.008868107062238052 +/- 0.0016771884713248407</t>
+          <t>-0.010351499516285112 +/- 0.0008215246180494683</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-0.0009029345372460806 +/- 0.0008384392131570486</t>
+          <t>-9.67429861335467e-05 +/- 0.0006772009029345308</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-3.2247662044537774e-05 +/- 0.0008586602357752163</t>
+          <t>-0.002676555949693682 +/- 0.0006457589292002935</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.0140277329893583 +/- 0.0015347312524077114</t>
+          <t>-0.005546597871654324 +/- 0.0014407164078483342</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.00048371493066748925 +/- 0.0017618559664169843</t>
+          <t>-0.003192518542405709 +/- 0.001102568268125045</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-0.0031925185424057203 +/- 0.0017392823682891704</t>
+          <t>0.0008061915511125117 +/- 0.0013547856522154258</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>-0.00012899064817806227 +/- 0.0021448937953325894</t>
+          <t>0.0021928410190260707 +/- 0.0022004156219583362</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.000838439213156994 +/- 0.0012915178584005625</t>
+          <t>0.0029345372460496287 +/- 0.0009058092167164296</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>0.0009674298613350119 +/- 0.0012818192140826733</t>
+          <t>-0.001515640116091621 +/- 0.0015265785718857972</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>0.0001934859722669602 +/- 0.0003590947670319127</t>
+          <t>-0.0003869719445340758 +/- 0.0006733509518807147</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>-0.002096098032892646 +/- 0.0011286681715575468</t>
+          <t>0.0016446307642695613 +/- 0.001473898082170468</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>-0.0011609158336021274 +/- 0.0016328911836403926</t>
+          <t>0.005740083843921284 +/- 0.0011245144001394943</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-0.007545952918413446 +/- 0.0017850180590903819</t>
+          <t>-0.007674943566591463 +/- 0.0016430492360989335</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-0.0014833924540471276 +/- 0.0009907959687673006</t>
+          <t>0.002515317639471093 +/- 0.0014334802174068289</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>0.0004514672686229848 +/- 0.0006481699852383821</t>
+          <t>-0.0010319251854240985 +/- 0.0006886216221883998</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>-0.0011931634956465985 +/- 0.000865896264566118</t>
+          <t>-0.0018381167365366323 +/- 0.0005594760262140365</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.0019026120606255525 +/- 0.0003366754759403675</t>
+          <t>-9.67429861335245e-05 +/- 0.0002064857864376873</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-0.0025798129635601686 +/- 0.0012572453201946505</t>
+          <t>0.0027732989358271063 +/- 0.0009587919217877082</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-0.007739438890680461 +/- 0.0017305911467267135</t>
+          <t>-0.0058045791680103485 +/- 0.0008284574381596472</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4731,92 +4731,92 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>-0.0005804579168010471 +/- 0.0005732469795108414</t>
+          <t>-0.00012899064817802896 +/- 0.0003590947670319326</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>0.00141889712995803 +/- 0.0011464939590216932</t>
+          <t>0.0005482102547564982 +/- 0.0012156128232809187</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>-0.005611093195743344 +/- 0.001414492886131018</t>
+          <t>0.00125765881973553 +/- 0.0015495664336322445</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.00025798129635598024 +/- 0.0013666314156992577</t>
+          <t>-0.002612060625604673 +/- 0.0006521686041972577</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-0.0013221541438246053 +/- 0.0016534593670808572</t>
+          <t>0.002063850370848086 +/- 0.0009802440602109301</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-0.0016768784263141324 +/- 0.0019920600079304032</t>
+          <t>-0.0020316027088036594 +/- 0.0012822247889113935</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>0.005417607223476261 +/- 0.0011874848525973568</t>
+          <t>0.005611093195743299 +/- 0.0016830684747758565</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-0.001225411157691103 +/- 0.0017112543258847536</t>
+          <t>-0.002160593356981655 +/- 0.0008036075971865284</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>-9.67429861335356e-05 +/- 0.00025186229203180135</t>
+          <t>6.449532408896453e-05 +/- 0.0003159612696269608</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>-0.0005804579168010692 +/- 0.0018513640882821477</t>
+          <t>0.0030635278942276354 +/- 0.0017500114222786442</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>-4.4408920985006264e-17 +/- 0.0012899064817800704</t>
+          <t>-0.003643985811028749 +/- 0.0012241375618253485</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-0.0028700419219606864 +/- 0.0009058092167164121</t>
+          <t>0.0013544018058690322 +/- 0.0009759913544289907</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>-0.0038052241212512385 +/- 0.0015652578006464491</t>
+          <t>-0.0005804579168010804 +/- 0.0012389147186261523</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>-0.0015156401160916321 +/- 0.000978651461173398</t>
+          <t>0.0002579812963559691 +/- 0.0015042765288217422</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>-0.004933892292808795 +/- 0.0012659004467197984</t>
+          <t>-0.0019993550467591547 +/- 0.0010868945208869652</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>-3.3306690738754695e-17 +/- 0.00024978931610493866</t>
+          <t>-0.0002902289584005402 +/- 0.00033667547594038767</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>0.00025798129635598024 +/- 0.0007603886567269628</t>
+          <t>6.449532408897563e-05 +/- 0.00034731794950881975</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>-0.0006772009029345604 +/- 0.000508859523961927</t>
+          <t>-0.0011286681715575897 +/- 0.0006802651760634836</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>6.449532408895343e-05 +/- 0.0006084476705615389</t>
+          <t>-0.0007739438890680739 +/- 0.00048263881157999616</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>-0.0002902289584005735 +/- 0.0010641728474685645</t>
+          <t>0.001547887778136059 +/- 0.0009865887481959738</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -4841,37 +4841,37 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>0.0013221541438245387 +/- 0.0006679237399938169</t>
+          <t>0.0008384392131570051 +/- 0.00032886291606534735</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>-3.3306690738754695e-17 +/- 0.0009006281872795265</t>
+          <t>-0.0009029345372460918 +/- 0.000800365923636948</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>-0.006191551112544347 +/- 0.0013513271099488443</t>
+          <t>-0.0021283456949371506 +/- 0.001250610733935212</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>0.0002902289584004847 +/- 0.00041921960657851113</t>
+          <t>-0.001064172847468603 +/- 0.0009786514611733951</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>0.003901967107384674 +/- 0.0011577763992916008</t>
+          <t>0.0034504998387616557 +/- 0.0012740887626661401</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>-0.00032247662044505577 +/- 0.0016880041700486905</t>
+          <t>-0.0015801354401806188 +/- 0.0010141364200913472</t>
         </is>
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>0.001483392454047039 +/- 0.0010907149000507765</t>
+          <t>-0.0006127055788455848 +/- 0.0007555868760954533</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.0063120794617110175 +/- 0.0014332758248218557</t>
+          <t>0.0034924703620634267 +/- 0.0008410384330923745</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4891,157 +4891,157 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.0014738865748157193 +/- 0.0018417312224543406</t>
+          <t>0.005254726049343172 +/- 0.0017851186513533023</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.0004806151874399478 +/- 0.001497724561681552</t>
+          <t>-0.007145145786606855 +/- 0.001634091637295728</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.004870233899391241 +/- 0.001718306655276122</t>
+          <t>-0.004613905799423268 +/- 0.0019181838573656728</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-0.0034604293495674177 +/- 0.0014669046000973492</t>
+          <t>-0.0007049022749119005 +/- 0.0014457563822721543</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.0020506247997437053 +/- 0.0016033317530530912</t>
+          <t>-0.004613905799423246 +/- 0.0020873434764373455</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0007369432874079207 +/- 0.0003524511374559366</t>
+          <t>0.0001281640499839587 +/- 0.0003567936150483703</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.002659404037167601 +/- 0.001173331203050322</t>
+          <t>-0.00208266581223967 +/- 0.0017911470502241188</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.019769304710028857 +/- 0.003363695951713035</t>
+          <t>0.006952899711630889 +/- 0.002961151259355861</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.013745594360781831 +/- 0.0030445706600254648</t>
+          <t>0.005222685036847164 +/- 0.002950731975608538</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.011630887536046164 +/- 0.0010137322665527998</t>
+          <t>0.0013777635373277586 +/- 0.0014825678053520175</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>-0.0008330663248958259 +/- 0.0011833505487099836</t>
+          <t>-0.01137455943607817 +/- 0.001690903531170605</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.008490868311438683 +/- 0.0016848211246568276</t>
+          <t>-0.007401473886574817 +/- 0.0016303177485688504</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.014418455623197712 +/- 0.0011099332313802572</t>
+          <t>0.006920858699134891 +/- 0.001368417590776204</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.005607177186799139 +/- 0.0028952383707805426</t>
+          <t>0.0029477731496315275 +/- 0.0015486121081184922</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0.00435757769945534 +/- 0.0017619643812710778</t>
+          <t>0.003396347324575466 +/- 0.0012832415504325974</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0.002499198974687633 +/- 0.0010987778404025542</t>
+          <t>-0.0025953220121755936 +/- 0.0012772272622873888</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>0.0021147068247356904 +/- 0.001531278839519172</t>
+          <t>-0.005318808074335157 +/- 0.0010742104847318377</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>0.0016661326497917628 +/- 0.0011355363759480354</t>
+          <t>-0.0018904197372637045 +/- 0.0015127294628789242</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-0.0001922460749759325 +/- 0.00038449214995192973</t>
+          <t>-6.4082024991996e-05 +/- 0.00019224607497598799</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.01919256648510097 +/- 0.002033784181039199</t>
+          <t>0.009580262736302459 +/- 0.0023125088850709436</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>0.00669657161166296 +/- 0.0009765940822895319</t>
+          <t>0.0030118551746235343 +/- 0.0014836061394155968</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>0.004613905799423279 +/- 0.0013981047247210098</t>
+          <t>-0.0004806151874399145 +/- 0.001463050311673304</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.002755527074655595 +/- 0.0015446293871443798</t>
+          <t>-0.0017302146747837255 +/- 0.0014343498420762099</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.0034924703620634713 +/- 0.001285240058963866</t>
+          <t>0.0018583787247677176 +/- 0.0009264230884204456</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.0006728612624159247 +/- 0.0007907057147871168</t>
+          <t>-0.00038449214995193157 +/- 0.0005323052779825783</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>0.007177186799102897 +/- 0.001678410875194975</t>
+          <t>-0.00817045818647869 +/- 0.0016100409517976171</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0.0003204101249599689 +/- 0.0014960099365496696</t>
+          <t>0.0037487984620313995 +/- 0.0022154686207065026</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>0.006344120474207004 +/- 0.00137291158510919</t>
+          <t>0.0019224607497596914 +/- 0.0008597505841075656</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.012880487023389975 +/- 0.0020655894215041346</t>
+          <t>0.001121435437359819 +/- 0.0020327743576497104</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0002242870874720082 +/- 0.0004763238944991349</t>
+          <t>0.00019224607497596579 +/- 0.0006278730516586168</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>3.20410124960202e-05 +/- 0.00048486850209616007</t>
+          <t>-0.0004165331624479296 +/- 0.0004542597526035819</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -5051,122 +5051,122 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.008426786286446686 +/- 0.001510012389355756</t>
+          <t>0.005126561999359192 +/- 0.002144594749206228</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.00893944248638262 +/- 0.001572623030029862</t>
+          <t>0.0004165331624479518 +/- 0.0016528318329418763</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>0.0028196090996475687 +/- 0.0005323052779825623</t>
+          <t>-0.0016020506247997445 +/- 0.0005549666156901141</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>6.408202499200711e-05 +/- 0.0006690359826280342</t>
+          <t>0.000961230374879829 +/- 0.001155255134720915</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>0.0018904197372637487 +/- 0.0010765970917277557</t>
+          <t>-9.6123037487994e-05 +/- 0.001173331203050345</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>0.0013777635373278252 +/- 0.000848330810309119</t>
+          <t>-0.0007049022749118783 +/- 0.001788565938731533</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>0.0017942966997757438 +/- 0.0009085195052071598</t>
+          <t>0.0003204101249599356 +/- 0.0006872031589082681</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.0019545017622557225 +/- 0.001076597091727738</t>
+          <t>0.0010253123998718362 +/- 0.001222607114920806</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.002851650112143567 +/- 0.0012280530532993786</t>
+          <t>3.2041012495998e-05 +/- 0.001308984185569721</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.008394745273950687 +/- 0.0019426474067573399</t>
+          <t>-0.002210829862223629 +/- 0.0015462901008668653</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.004549823774431283 +/- 0.002085375212466891</t>
+          <t>0.0007689842999038965 +/- 0.0017502723849724719</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.0076578019865428115 +/- 0.0013245771617170486</t>
+          <t>0.00733739186158282 +/- 0.001443268904781181</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.004005126561999373 +/- 0.0012263799557196157</t>
+          <t>-0.004549823774431261 +/- 0.0009374392078390177</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>0.0006087792374239287 +/- 0.0011592471973806869</t>
+          <t>0.003140019224607482 +/- 0.0012800374466797968</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-3.2041012495942486e-05 +/- 0.000525511677887091</t>
+          <t>-0.00038449214995193157 +/- 0.0006842087953880885</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>0.011054149311118266 +/- 0.0016036518751992577</t>
+          <t>0.0005767382249279085 +/- 0.002015275257099196</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>-0.00176225568727969 +/- 0.0017505656366097666</t>
+          <t>0.0015059275873117507 +/- 0.0015369669920168355</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-0.0023069528997116005 +/- 0.0020152752570991844</t>
+          <t>-0.0010573534123678341 +/- 0.0014404208133924486</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.008907401473886589 +/- 0.0016759624262252032</t>
+          <t>-0.0006408202499199045 +/- 0.002021379083061525</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>0.0003204101249599689 +/- 0.0006872031589082681</t>
+          <t>0.0001602050624799789 +/- 0.0006909278645577571</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.0001922460749759991 +/- 0.0007049022749118823</t>
+          <t>0.0008971483498878662 +/- 0.0007555159322365709</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>-3.20410124959869e-05 +/- 9.612303748796071e-05</t>
+          <t>0.0001281640499839698 +/- 0.00041032516740996476</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>0.005703300224287122 +/- 0.0013426675321856355</t>
+          <t>0.003268183274591463 +/- 0.0017479246007030972</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.007145145786606888 +/- 0.0016957537484651568</t>
+          <t>-0.004645946811919255 +/- 0.0028774541830345443</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5176,107 +5176,107 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>0.0006728612624159136 +/- 0.0006789368824228274</t>
+          <t>-0.0011855174623518038 +/- 0.000883890690428291</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>0.004710028836911273 +/- 0.0019909306482417243</t>
+          <t>0.003492470362063438 +/- 0.0011503571336761455</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>0.008426786286446686 +/- 0.0015100123893557326</t>
+          <t>-0.0017622556872797235 +/- 0.001383711815552009</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.0030438961871195325 +/- 0.00038582488237077497</t>
+          <t>0.0025312399871835756 +/- 0.000615487751114969</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.004806151874399267 +/- 0.0010722973746031138</t>
+          <t>-0.004581864786927248 +/- 0.0008112136431382383</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>0.004742069849407282 +/- 0.0015285947378246283</t>
+          <t>-0.0009612303748798512 +/- 0.0010912775626995602</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>0.009195770586350571 +/- 0.0016214778505453486</t>
+          <t>0.0010253123998718362 +/- 0.0017712624109048843</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>0.005222685036847185 +/- 0.0006254156134553971</t>
+          <t>0.004069208586991335 +/- 0.0017017970810495814</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>0.0003844921499519538 +/- 0.00031393652582929814</t>
+          <t>-0.000128164049983992 +/- 0.00021253603270462822</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>0.012495994873438032 +/- 0.002154147557061412</t>
+          <t>0.0031400192246075153 +/- 0.0019052955779965976</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.005799423261775105 +/- 0.0009553381298222122</t>
+          <t>0.002435116949695615 +/- 0.0011919945682626304</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.000352451137455978 +/- 0.0017162142570768214</t>
+          <t>0.00221082986222364 +/- 0.0015329540165210944</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>0.009452098686318532 +/- 0.0026392538109850836</t>
+          <t>0.009163729573854518 +/- 0.0018803461392016803</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>0.006408202499199001 +/- 0.0015631286020699232</t>
+          <t>0.0049343159243832035 +/- 0.0011833505487099836</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>0.012239666773470081 +/- 0.0019947942859690117</t>
+          <t>0.005927587311759064 +/- 0.0017209931434790946</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>-6.408202499192938e-05 +/- 0.00031393652582928453</t>
+          <t>-0.0001281640499839698 +/- 0.0003267554959046933</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>0.0027875680871515818 +/- 0.0008721984997639439</t>
+          <t>-0.0005767382249279085 +/- 0.001041209664163535</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>0.0005126561999359458 +/- 0.0005206048320817568</t>
+          <t>0.0019224607497597024 +/- 0.0010233078771336838</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
         <is>
-          <t>0.000192246074975988 +/- 0.00015696826291466948</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>0.000352451137455978 +/- 0.0007228781911360539</t>
+          <t>0.0006087792374238843 +/- 0.0005255116778870964</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>0.01531560397308559 +/- 0.0016262194861197574</t>
+          <t>-6.40820249919849e-05 +/- 0.0016759624262251789</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5286,37 +5286,37 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>0.0001602050624800122 +/- 0.0006286900631319627</t>
+          <t>-0.0003844921499519538 +/- 0.00023977298217069557</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>-0.00028836911246391537 +/- 0.0016240084456871772</t>
+          <t>0.004037167574495348 +/- 0.001616087178842479</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>0.007529637936558831 +/- 0.0013612717581703258</t>
+          <t>0.004357577699455328 +/- 0.0013303774105752426</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>0.0008651073373918794 +/- 0.0005916752743550057</t>
+          <t>0.0008330663248958703 +/- 0.0008739623003515372</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>0.013168856135853913 +/- 0.0019141655919569134</t>
+          <t>0.0013457225248317938 +/- 0.0018113802018715091</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>0.019384812560076937 +/- 0.0016227436414098697</t>
+          <t>0.0149631528356296 +/- 0.0014260950390431056</t>
         </is>
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>0.006247997436719044 +/- 0.0012095216974160172</t>
+          <t>-0.0029477731496315275 +/- 0.0018781609599170636</t>
         </is>
       </c>
     </row>
